--- a/2022 data/excel_outputs/298_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/298_boothwise_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="742">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="398">
   <si>
     <t>Booth No.</t>
   </si>
@@ -64,1179 +64,6 @@
     <t>TURNOUT %</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>53</t>
-  </si>
-  <si>
-    <t>54</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>58</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>61</t>
-  </si>
-  <si>
-    <t>62</t>
-  </si>
-  <si>
-    <t>63</t>
-  </si>
-  <si>
-    <t>64</t>
-  </si>
-  <si>
-    <t>65</t>
-  </si>
-  <si>
-    <t>66</t>
-  </si>
-  <si>
-    <t>67</t>
-  </si>
-  <si>
-    <t>68</t>
-  </si>
-  <si>
-    <t>69</t>
-  </si>
-  <si>
-    <t>70</t>
-  </si>
-  <si>
-    <t>71</t>
-  </si>
-  <si>
-    <t>72</t>
-  </si>
-  <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>74</t>
-  </si>
-  <si>
-    <t>75</t>
-  </si>
-  <si>
-    <t>76</t>
-  </si>
-  <si>
-    <t>77</t>
-  </si>
-  <si>
-    <t>78</t>
-  </si>
-  <si>
-    <t>79</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>81</t>
-  </si>
-  <si>
-    <t>82</t>
-  </si>
-  <si>
-    <t>83</t>
-  </si>
-  <si>
-    <t>84</t>
-  </si>
-  <si>
-    <t>85</t>
-  </si>
-  <si>
-    <t>86</t>
-  </si>
-  <si>
-    <t>87</t>
-  </si>
-  <si>
-    <t>88</t>
-  </si>
-  <si>
-    <t>89</t>
-  </si>
-  <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>91</t>
-  </si>
-  <si>
-    <t>92</t>
-  </si>
-  <si>
-    <t>93</t>
-  </si>
-  <si>
-    <t>94</t>
-  </si>
-  <si>
-    <t>95</t>
-  </si>
-  <si>
-    <t>96</t>
-  </si>
-  <si>
-    <t>97</t>
-  </si>
-  <si>
-    <t>98</t>
-  </si>
-  <si>
-    <t>99</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>113</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>116</t>
-  </si>
-  <si>
-    <t>117</t>
-  </si>
-  <si>
-    <t>118</t>
-  </si>
-  <si>
-    <t>119</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>122</t>
-  </si>
-  <si>
-    <t>123</t>
-  </si>
-  <si>
-    <t>124</t>
-  </si>
-  <si>
-    <t>125</t>
-  </si>
-  <si>
-    <t>126</t>
-  </si>
-  <si>
-    <t>127</t>
-  </si>
-  <si>
-    <t>128</t>
-  </si>
-  <si>
-    <t>129</t>
-  </si>
-  <si>
-    <t>130</t>
-  </si>
-  <si>
-    <t>131</t>
-  </si>
-  <si>
-    <t>132</t>
-  </si>
-  <si>
-    <t>133</t>
-  </si>
-  <si>
-    <t>134</t>
-  </si>
-  <si>
-    <t>135</t>
-  </si>
-  <si>
-    <t>136</t>
-  </si>
-  <si>
-    <t>137</t>
-  </si>
-  <si>
-    <t>138</t>
-  </si>
-  <si>
-    <t>139</t>
-  </si>
-  <si>
-    <t>140</t>
-  </si>
-  <si>
-    <t>141</t>
-  </si>
-  <si>
-    <t>142</t>
-  </si>
-  <si>
-    <t>143</t>
-  </si>
-  <si>
-    <t>144</t>
-  </si>
-  <si>
-    <t>145</t>
-  </si>
-  <si>
-    <t>146</t>
-  </si>
-  <si>
-    <t>147</t>
-  </si>
-  <si>
-    <t>148</t>
-  </si>
-  <si>
-    <t>149</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>151</t>
-  </si>
-  <si>
-    <t>152</t>
-  </si>
-  <si>
-    <t>153</t>
-  </si>
-  <si>
-    <t>154</t>
-  </si>
-  <si>
-    <t>155</t>
-  </si>
-  <si>
-    <t>156</t>
-  </si>
-  <si>
-    <t>157</t>
-  </si>
-  <si>
-    <t>158</t>
-  </si>
-  <si>
-    <t>159</t>
-  </si>
-  <si>
-    <t>160</t>
-  </si>
-  <si>
-    <t>161</t>
-  </si>
-  <si>
-    <t>162</t>
-  </si>
-  <si>
-    <t>163</t>
-  </si>
-  <si>
-    <t>164</t>
-  </si>
-  <si>
-    <t>165</t>
-  </si>
-  <si>
-    <t>166</t>
-  </si>
-  <si>
-    <t>167</t>
-  </si>
-  <si>
-    <t>168</t>
-  </si>
-  <si>
-    <t>169</t>
-  </si>
-  <si>
-    <t>170</t>
-  </si>
-  <si>
-    <t>171</t>
-  </si>
-  <si>
-    <t>172</t>
-  </si>
-  <si>
-    <t>173</t>
-  </si>
-  <si>
-    <t>174</t>
-  </si>
-  <si>
-    <t>175</t>
-  </si>
-  <si>
-    <t>176</t>
-  </si>
-  <si>
-    <t>177</t>
-  </si>
-  <si>
-    <t>178</t>
-  </si>
-  <si>
-    <t>179</t>
-  </si>
-  <si>
-    <t>180</t>
-  </si>
-  <si>
-    <t>181</t>
-  </si>
-  <si>
-    <t>182</t>
-  </si>
-  <si>
-    <t>183</t>
-  </si>
-  <si>
-    <t>184</t>
-  </si>
-  <si>
-    <t>185</t>
-  </si>
-  <si>
-    <t>186</t>
-  </si>
-  <si>
-    <t>187</t>
-  </si>
-  <si>
-    <t>188</t>
-  </si>
-  <si>
-    <t>189</t>
-  </si>
-  <si>
-    <t>190</t>
-  </si>
-  <si>
-    <t>191</t>
-  </si>
-  <si>
-    <t>192</t>
-  </si>
-  <si>
-    <t>193</t>
-  </si>
-  <si>
-    <t>194</t>
-  </si>
-  <si>
-    <t>195</t>
-  </si>
-  <si>
-    <t>196</t>
-  </si>
-  <si>
-    <t>197</t>
-  </si>
-  <si>
-    <t>198</t>
-  </si>
-  <si>
-    <t>199</t>
-  </si>
-  <si>
-    <t>200</t>
-  </si>
-  <si>
-    <t>201</t>
-  </si>
-  <si>
-    <t>202</t>
-  </si>
-  <si>
-    <t>203</t>
-  </si>
-  <si>
-    <t>204</t>
-  </si>
-  <si>
-    <t>205</t>
-  </si>
-  <si>
-    <t>206</t>
-  </si>
-  <si>
-    <t>207</t>
-  </si>
-  <si>
-    <t>208</t>
-  </si>
-  <si>
-    <t>209</t>
-  </si>
-  <si>
-    <t>210</t>
-  </si>
-  <si>
-    <t>211</t>
-  </si>
-  <si>
-    <t>212</t>
-  </si>
-  <si>
-    <t>213</t>
-  </si>
-  <si>
-    <t>214</t>
-  </si>
-  <si>
-    <t>215</t>
-  </si>
-  <si>
-    <t>216</t>
-  </si>
-  <si>
-    <t>217</t>
-  </si>
-  <si>
-    <t>218</t>
-  </si>
-  <si>
-    <t>219</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>221</t>
-  </si>
-  <si>
-    <t>222</t>
-  </si>
-  <si>
-    <t>223</t>
-  </si>
-  <si>
-    <t>224</t>
-  </si>
-  <si>
-    <t>225</t>
-  </si>
-  <si>
-    <t>226</t>
-  </si>
-  <si>
-    <t>227</t>
-  </si>
-  <si>
-    <t>228</t>
-  </si>
-  <si>
-    <t>229</t>
-  </si>
-  <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>231</t>
-  </si>
-  <si>
-    <t>232</t>
-  </si>
-  <si>
-    <t>233</t>
-  </si>
-  <si>
-    <t>234</t>
-  </si>
-  <si>
-    <t>235</t>
-  </si>
-  <si>
-    <t>236</t>
-  </si>
-  <si>
-    <t>237</t>
-  </si>
-  <si>
-    <t>238</t>
-  </si>
-  <si>
-    <t>239</t>
-  </si>
-  <si>
-    <t>240</t>
-  </si>
-  <si>
-    <t>241</t>
-  </si>
-  <si>
-    <t>242</t>
-  </si>
-  <si>
-    <t>243</t>
-  </si>
-  <si>
-    <t>244</t>
-  </si>
-  <si>
-    <t>245</t>
-  </si>
-  <si>
-    <t>246</t>
-  </si>
-  <si>
-    <t>247</t>
-  </si>
-  <si>
-    <t>248</t>
-  </si>
-  <si>
-    <t>249</t>
-  </si>
-  <si>
-    <t>250</t>
-  </si>
-  <si>
-    <t>251</t>
-  </si>
-  <si>
-    <t>252</t>
-  </si>
-  <si>
-    <t>253</t>
-  </si>
-  <si>
-    <t>254</t>
-  </si>
-  <si>
-    <t>255</t>
-  </si>
-  <si>
-    <t>256</t>
-  </si>
-  <si>
-    <t>257</t>
-  </si>
-  <si>
-    <t>258</t>
-  </si>
-  <si>
-    <t>259</t>
-  </si>
-  <si>
-    <t>260</t>
-  </si>
-  <si>
-    <t>261</t>
-  </si>
-  <si>
-    <t>262</t>
-  </si>
-  <si>
-    <t>263</t>
-  </si>
-  <si>
-    <t>264</t>
-  </si>
-  <si>
-    <t>265</t>
-  </si>
-  <si>
-    <t>266</t>
-  </si>
-  <si>
-    <t>267</t>
-  </si>
-  <si>
-    <t>268</t>
-  </si>
-  <si>
-    <t>269</t>
-  </si>
-  <si>
-    <t>270</t>
-  </si>
-  <si>
-    <t>271</t>
-  </si>
-  <si>
-    <t>272</t>
-  </si>
-  <si>
-    <t>273</t>
-  </si>
-  <si>
-    <t>274</t>
-  </si>
-  <si>
-    <t>275</t>
-  </si>
-  <si>
-    <t>276</t>
-  </si>
-  <si>
-    <t>277</t>
-  </si>
-  <si>
-    <t>278</t>
-  </si>
-  <si>
-    <t>279</t>
-  </si>
-  <si>
-    <t>280</t>
-  </si>
-  <si>
-    <t>281</t>
-  </si>
-  <si>
-    <t>282</t>
-  </si>
-  <si>
-    <t>283</t>
-  </si>
-  <si>
-    <t>284</t>
-  </si>
-  <si>
-    <t>285</t>
-  </si>
-  <si>
-    <t>286</t>
-  </si>
-  <si>
-    <t>287</t>
-  </si>
-  <si>
-    <t>288</t>
-  </si>
-  <si>
-    <t>289</t>
-  </si>
-  <si>
-    <t>290</t>
-  </si>
-  <si>
-    <t>291</t>
-  </si>
-  <si>
-    <t>292</t>
-  </si>
-  <si>
-    <t>293</t>
-  </si>
-  <si>
-    <t>294</t>
-  </si>
-  <si>
-    <t>295</t>
-  </si>
-  <si>
-    <t>296</t>
-  </si>
-  <si>
-    <t>297</t>
-  </si>
-  <si>
-    <t>298</t>
-  </si>
-  <si>
-    <t>299</t>
-  </si>
-  <si>
-    <t>300</t>
-  </si>
-  <si>
-    <t>301</t>
-  </si>
-  <si>
-    <t>302</t>
-  </si>
-  <si>
-    <t>303</t>
-  </si>
-  <si>
-    <t>304</t>
-  </si>
-  <si>
-    <t>305</t>
-  </si>
-  <si>
-    <t>306</t>
-  </si>
-  <si>
-    <t>307</t>
-  </si>
-  <si>
-    <t>308</t>
-  </si>
-  <si>
-    <t>309</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>311</t>
-  </si>
-  <si>
-    <t>312</t>
-  </si>
-  <si>
-    <t>313</t>
-  </si>
-  <si>
-    <t>314</t>
-  </si>
-  <si>
-    <t>315</t>
-  </si>
-  <si>
-    <t>316</t>
-  </si>
-  <si>
-    <t>317</t>
-  </si>
-  <si>
-    <t>318</t>
-  </si>
-  <si>
-    <t>319</t>
-  </si>
-  <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>321</t>
-  </si>
-  <si>
-    <t>322</t>
-  </si>
-  <si>
-    <t>323</t>
-  </si>
-  <si>
-    <t>324</t>
-  </si>
-  <si>
-    <t>325</t>
-  </si>
-  <si>
-    <t>326</t>
-  </si>
-  <si>
-    <t>327</t>
-  </si>
-  <si>
-    <t>328</t>
-  </si>
-  <si>
-    <t>329</t>
-  </si>
-  <si>
-    <t>330</t>
-  </si>
-  <si>
-    <t>331</t>
-  </si>
-  <si>
-    <t>332</t>
-  </si>
-  <si>
-    <t>333</t>
-  </si>
-  <si>
-    <t>334</t>
-  </si>
-  <si>
-    <t>335</t>
-  </si>
-  <si>
-    <t>336</t>
-  </si>
-  <si>
-    <t>337</t>
-  </si>
-  <si>
-    <t>338</t>
-  </si>
-  <si>
-    <t>339</t>
-  </si>
-  <si>
-    <t>340</t>
-  </si>
-  <si>
-    <t>341</t>
-  </si>
-  <si>
-    <t>342</t>
-  </si>
-  <si>
-    <t>343</t>
-  </si>
-  <si>
-    <t>344</t>
-  </si>
-  <si>
-    <t>345</t>
-  </si>
-  <si>
-    <t>346</t>
-  </si>
-  <si>
-    <t>347</t>
-  </si>
-  <si>
-    <t>348</t>
-  </si>
-  <si>
-    <t>349</t>
-  </si>
-  <si>
-    <t>350</t>
-  </si>
-  <si>
-    <t>351</t>
-  </si>
-  <si>
-    <t>352</t>
-  </si>
-  <si>
-    <t>353</t>
-  </si>
-  <si>
-    <t>354</t>
-  </si>
-  <si>
-    <t>355</t>
-  </si>
-  <si>
-    <t>356</t>
-  </si>
-  <si>
-    <t>357</t>
-  </si>
-  <si>
-    <t>358</t>
-  </si>
-  <si>
-    <t>359</t>
-  </si>
-  <si>
-    <t>360</t>
-  </si>
-  <si>
-    <t>361</t>
-  </si>
-  <si>
-    <t>362</t>
-  </si>
-  <si>
-    <t>363</t>
-  </si>
-  <si>
-    <t>364</t>
-  </si>
-  <si>
-    <t>365</t>
-  </si>
-  <si>
-    <t>366</t>
-  </si>
-  <si>
-    <t>367</t>
-  </si>
-  <si>
-    <t>368</t>
-  </si>
-  <si>
-    <t>369</t>
-  </si>
-  <si>
-    <t>370</t>
-  </si>
-  <si>
-    <t>371</t>
-  </si>
-  <si>
-    <t>372</t>
-  </si>
-  <si>
-    <t>373</t>
-  </si>
-  <si>
-    <t>374</t>
-  </si>
-  <si>
-    <t>375</t>
-  </si>
-  <si>
-    <t>376</t>
-  </si>
-  <si>
-    <t>377</t>
-  </si>
-  <si>
-    <t>378</t>
-  </si>
-  <si>
-    <t>379</t>
-  </si>
-  <si>
-    <t>380</t>
-  </si>
-  <si>
-    <t>381</t>
-  </si>
-  <si>
-    <t>382</t>
-  </si>
-  <si>
-    <t>383</t>
-  </si>
-  <si>
-    <t>384</t>
-  </si>
-  <si>
-    <t>385</t>
-  </si>
-  <si>
-    <t>386</t>
-  </si>
-  <si>
-    <t>387</t>
-  </si>
-  <si>
-    <t>388</t>
-  </si>
-  <si>
-    <t>389</t>
-  </si>
-  <si>
-    <t>390</t>
-  </si>
-  <si>
-    <t>391</t>
-  </si>
-  <si>
     <t>izk0 ik0 n0 Hkkx txUukFkiqj xzUV</t>
   </si>
   <si>
@@ -2240,6 +1067,147 @@
   </si>
   <si>
     <t xml:space="preserve">izk0ik0 lksgkal </t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM NO. 345</t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM ROOM NO. 346</t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM ROOM ROOM NO. 347</t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM ROOM ROOM ROOM NO. 348</t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM ROOM ROOM ROOM ROOM NO. 349</t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM ROOM ROOM ROOM ROOM ROOM NO. 350</t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 351</t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 352</t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 353</t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 354</t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 355</t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 356</t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 357</t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 358</t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 359</t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 360</t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 361</t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 362</t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 363</t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 364</t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 365</t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 366</t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 367</t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 368</t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 369</t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 370</t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 371</t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 372</t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 373</t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 374</t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 375</t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 376</t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 377</t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 378</t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 379</t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 380</t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 381</t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 382</t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 383</t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 384</t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 385</t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 386</t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 387</t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 388</t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 389</t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 390</t>
+  </si>
+  <si>
+    <t>izk0ik0 lksgkal ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 391</t>
   </si>
 </sst>
 </file>
@@ -2651,11 +1619,11 @@
       </c>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" t="s">
+      <c r="A2">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
         <v>16</v>
-      </c>
-      <c r="B2" t="s">
-        <v>407</v>
       </c>
       <c r="C2">
         <v>11</v>
@@ -2698,11 +1666,11 @@
       </c>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" t="s">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
         <v>17</v>
-      </c>
-      <c r="B3" t="s">
-        <v>408</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -2745,11 +1713,11 @@
       </c>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" t="s">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
         <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>407</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -2792,11 +1760,11 @@
       </c>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" t="s">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
         <v>18</v>
-      </c>
-      <c r="B5" t="s">
-        <v>409</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -2839,11 +1807,11 @@
       </c>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" t="s">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
         <v>19</v>
-      </c>
-      <c r="B6" t="s">
-        <v>410</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -2886,11 +1854,11 @@
       </c>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" t="s">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
         <v>20</v>
-      </c>
-      <c r="B7" t="s">
-        <v>411</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -2933,11 +1901,11 @@
       </c>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" t="s">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
         <v>21</v>
-      </c>
-      <c r="B8" t="s">
-        <v>412</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -2980,11 +1948,11 @@
       </c>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" t="s">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
         <v>22</v>
-      </c>
-      <c r="B9" t="s">
-        <v>413</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -3027,11 +1995,11 @@
       </c>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" t="s">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
         <v>23</v>
-      </c>
-      <c r="B10" t="s">
-        <v>414</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -3074,11 +2042,11 @@
       </c>
     </row>
     <row r="11" spans="1:16">
-      <c r="A11" t="s">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
         <v>24</v>
-      </c>
-      <c r="B11" t="s">
-        <v>415</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -3121,11 +2089,11 @@
       </c>
     </row>
     <row r="12" spans="1:16">
-      <c r="A12" t="s">
-        <v>25</v>
+      <c r="A12">
+        <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>415</v>
+        <v>24</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -3168,11 +2136,11 @@
       </c>
     </row>
     <row r="13" spans="1:16">
-      <c r="A13" t="s">
-        <v>26</v>
+      <c r="A13">
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>416</v>
+        <v>25</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -3215,11 +2183,11 @@
       </c>
     </row>
     <row r="14" spans="1:16">
-      <c r="A14" t="s">
-        <v>27</v>
+      <c r="A14">
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>417</v>
+        <v>26</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -3262,11 +2230,11 @@
       </c>
     </row>
     <row r="15" spans="1:16">
-      <c r="A15" t="s">
-        <v>28</v>
+      <c r="A15">
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>418</v>
+        <v>27</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -3309,11 +2277,11 @@
       </c>
     </row>
     <row r="16" spans="1:16">
-      <c r="A16" t="s">
-        <v>29</v>
+      <c r="A16">
+        <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>419</v>
+        <v>28</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -3356,11 +2324,11 @@
       </c>
     </row>
     <row r="17" spans="1:15">
-      <c r="A17" t="s">
-        <v>30</v>
+      <c r="A17">
+        <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>420</v>
+        <v>29</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -3403,11 +2371,11 @@
       </c>
     </row>
     <row r="18" spans="1:15">
-      <c r="A18" t="s">
-        <v>31</v>
+      <c r="A18">
+        <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>421</v>
+        <v>30</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -3450,11 +2418,11 @@
       </c>
     </row>
     <row r="19" spans="1:15">
-      <c r="A19" t="s">
-        <v>32</v>
+      <c r="A19">
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>422</v>
+        <v>31</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -3497,11 +2465,11 @@
       </c>
     </row>
     <row r="20" spans="1:15">
-      <c r="A20" t="s">
-        <v>33</v>
+      <c r="A20">
+        <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>423</v>
+        <v>32</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -3544,11 +2512,11 @@
       </c>
     </row>
     <row r="21" spans="1:15">
-      <c r="A21" t="s">
-        <v>34</v>
+      <c r="A21">
+        <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>423</v>
+        <v>32</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -3591,11 +2559,11 @@
       </c>
     </row>
     <row r="22" spans="1:15">
-      <c r="A22" t="s">
-        <v>35</v>
+      <c r="A22">
+        <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>424</v>
+        <v>33</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -3638,11 +2606,11 @@
       </c>
     </row>
     <row r="23" spans="1:15">
-      <c r="A23" t="s">
-        <v>36</v>
+      <c r="A23">
+        <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>425</v>
+        <v>34</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -3685,11 +2653,11 @@
       </c>
     </row>
     <row r="24" spans="1:15">
-      <c r="A24" t="s">
-        <v>37</v>
+      <c r="A24">
+        <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>426</v>
+        <v>35</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -3732,11 +2700,11 @@
       </c>
     </row>
     <row r="25" spans="1:15">
-      <c r="A25" t="s">
-        <v>38</v>
+      <c r="A25">
+        <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>427</v>
+        <v>36</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -3779,11 +2747,11 @@
       </c>
     </row>
     <row r="26" spans="1:15">
-      <c r="A26" t="s">
-        <v>39</v>
+      <c r="A26">
+        <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>428</v>
+        <v>37</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -3826,11 +2794,11 @@
       </c>
     </row>
     <row r="27" spans="1:15">
-      <c r="A27" t="s">
-        <v>40</v>
+      <c r="A27">
+        <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>429</v>
+        <v>38</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -3873,11 +2841,11 @@
       </c>
     </row>
     <row r="28" spans="1:15">
-      <c r="A28" t="s">
-        <v>41</v>
+      <c r="A28">
+        <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>430</v>
+        <v>39</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -3920,11 +2888,11 @@
       </c>
     </row>
     <row r="29" spans="1:15">
-      <c r="A29" t="s">
-        <v>42</v>
+      <c r="A29">
+        <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>431</v>
+        <v>40</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -3967,11 +2935,11 @@
       </c>
     </row>
     <row r="30" spans="1:15">
-      <c r="A30" t="s">
-        <v>43</v>
+      <c r="A30">
+        <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>432</v>
+        <v>41</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -4014,11 +2982,11 @@
       </c>
     </row>
     <row r="31" spans="1:15">
-      <c r="A31" t="s">
-        <v>44</v>
+      <c r="A31">
+        <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>433</v>
+        <v>42</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -4061,11 +3029,11 @@
       </c>
     </row>
     <row r="32" spans="1:15">
-      <c r="A32" t="s">
-        <v>45</v>
+      <c r="A32">
+        <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>434</v>
+        <v>43</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -4108,11 +3076,11 @@
       </c>
     </row>
     <row r="33" spans="1:15">
-      <c r="A33" t="s">
-        <v>46</v>
+      <c r="A33">
+        <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>435</v>
+        <v>44</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -4155,11 +3123,11 @@
       </c>
     </row>
     <row r="34" spans="1:15">
-      <c r="A34" t="s">
-        <v>47</v>
+      <c r="A34">
+        <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>435</v>
+        <v>44</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -4202,11 +3170,11 @@
       </c>
     </row>
     <row r="35" spans="1:15">
-      <c r="A35" t="s">
-        <v>48</v>
+      <c r="A35">
+        <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>436</v>
+        <v>45</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -4249,11 +3217,11 @@
       </c>
     </row>
     <row r="36" spans="1:15">
-      <c r="A36" t="s">
-        <v>49</v>
+      <c r="A36">
+        <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>437</v>
+        <v>46</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -4296,11 +3264,11 @@
       </c>
     </row>
     <row r="37" spans="1:15">
-      <c r="A37" t="s">
-        <v>50</v>
+      <c r="A37">
+        <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>438</v>
+        <v>47</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -4343,11 +3311,11 @@
       </c>
     </row>
     <row r="38" spans="1:15">
-      <c r="A38" t="s">
-        <v>51</v>
+      <c r="A38">
+        <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>439</v>
+        <v>48</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -4390,11 +3358,11 @@
       </c>
     </row>
     <row r="39" spans="1:15">
-      <c r="A39" t="s">
-        <v>52</v>
+      <c r="A39">
+        <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>440</v>
+        <v>49</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -4437,11 +3405,11 @@
       </c>
     </row>
     <row r="40" spans="1:15">
-      <c r="A40" t="s">
-        <v>53</v>
+      <c r="A40">
+        <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>441</v>
+        <v>50</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -4484,11 +3452,11 @@
       </c>
     </row>
     <row r="41" spans="1:15">
-      <c r="A41" t="s">
-        <v>54</v>
+      <c r="A41">
+        <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>442</v>
+        <v>51</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -4531,11 +3499,11 @@
       </c>
     </row>
     <row r="42" spans="1:15">
-      <c r="A42" t="s">
-        <v>55</v>
+      <c r="A42">
+        <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>443</v>
+        <v>52</v>
       </c>
       <c r="C42">
         <v>1</v>
@@ -4578,11 +3546,11 @@
       </c>
     </row>
     <row r="43" spans="1:15">
-      <c r="A43" t="s">
-        <v>56</v>
+      <c r="A43">
+        <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>443</v>
+        <v>52</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -4625,11 +3593,11 @@
       </c>
     </row>
     <row r="44" spans="1:15">
-      <c r="A44" t="s">
-        <v>57</v>
+      <c r="A44">
+        <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>444</v>
+        <v>53</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -4672,11 +3640,11 @@
       </c>
     </row>
     <row r="45" spans="1:15">
-      <c r="A45" t="s">
-        <v>58</v>
+      <c r="A45">
+        <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>445</v>
+        <v>54</v>
       </c>
       <c r="C45">
         <v>1</v>
@@ -4719,11 +3687,11 @@
       </c>
     </row>
     <row r="46" spans="1:15">
-      <c r="A46" t="s">
-        <v>59</v>
+      <c r="A46">
+        <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>446</v>
+        <v>55</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -4766,11 +3734,11 @@
       </c>
     </row>
     <row r="47" spans="1:15">
-      <c r="A47" t="s">
-        <v>60</v>
+      <c r="A47">
+        <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>447</v>
+        <v>56</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -4813,11 +3781,11 @@
       </c>
     </row>
     <row r="48" spans="1:15">
-      <c r="A48" t="s">
-        <v>61</v>
+      <c r="A48">
+        <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>448</v>
+        <v>57</v>
       </c>
       <c r="C48">
         <v>1</v>
@@ -4860,11 +3828,11 @@
       </c>
     </row>
     <row r="49" spans="1:15">
-      <c r="A49" t="s">
-        <v>62</v>
+      <c r="A49">
+        <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>449</v>
+        <v>58</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -4907,11 +3875,11 @@
       </c>
     </row>
     <row r="50" spans="1:15">
-      <c r="A50" t="s">
-        <v>63</v>
+      <c r="A50">
+        <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>450</v>
+        <v>59</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -4954,11 +3922,11 @@
       </c>
     </row>
     <row r="51" spans="1:15">
-      <c r="A51" t="s">
-        <v>64</v>
+      <c r="A51">
+        <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>451</v>
+        <v>60</v>
       </c>
       <c r="C51">
         <v>1</v>
@@ -5001,11 +3969,11 @@
       </c>
     </row>
     <row r="52" spans="1:15">
-      <c r="A52" t="s">
-        <v>65</v>
+      <c r="A52">
+        <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>452</v>
+        <v>61</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -5048,11 +4016,11 @@
       </c>
     </row>
     <row r="53" spans="1:15">
-      <c r="A53" t="s">
-        <v>66</v>
+      <c r="A53">
+        <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>453</v>
+        <v>62</v>
       </c>
       <c r="C53">
         <v>1</v>
@@ -5095,11 +4063,11 @@
       </c>
     </row>
     <row r="54" spans="1:15">
-      <c r="A54" t="s">
-        <v>67</v>
+      <c r="A54">
+        <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>454</v>
+        <v>63</v>
       </c>
       <c r="C54">
         <v>1</v>
@@ -5142,11 +4110,11 @@
       </c>
     </row>
     <row r="55" spans="1:15">
-      <c r="A55" t="s">
-        <v>68</v>
+      <c r="A55">
+        <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>455</v>
+        <v>64</v>
       </c>
       <c r="C55">
         <v>1</v>
@@ -5189,11 +4157,11 @@
       </c>
     </row>
     <row r="56" spans="1:15">
-      <c r="A56" t="s">
-        <v>69</v>
+      <c r="A56">
+        <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>456</v>
+        <v>65</v>
       </c>
       <c r="C56">
         <v>1</v>
@@ -5236,11 +4204,11 @@
       </c>
     </row>
     <row r="57" spans="1:15">
-      <c r="A57" t="s">
-        <v>70</v>
+      <c r="A57">
+        <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>457</v>
+        <v>66</v>
       </c>
       <c r="C57">
         <v>1</v>
@@ -5283,11 +4251,11 @@
       </c>
     </row>
     <row r="58" spans="1:15">
-      <c r="A58" t="s">
-        <v>71</v>
+      <c r="A58">
+        <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>458</v>
+        <v>67</v>
       </c>
       <c r="C58">
         <v>1</v>
@@ -5330,11 +4298,11 @@
       </c>
     </row>
     <row r="59" spans="1:15">
-      <c r="A59" t="s">
-        <v>72</v>
+      <c r="A59">
+        <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>459</v>
+        <v>68</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -5377,11 +4345,11 @@
       </c>
     </row>
     <row r="60" spans="1:15">
-      <c r="A60" t="s">
-        <v>73</v>
+      <c r="A60">
+        <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>460</v>
+        <v>69</v>
       </c>
       <c r="C60">
         <v>1</v>
@@ -5424,11 +4392,11 @@
       </c>
     </row>
     <row r="61" spans="1:15">
-      <c r="A61" t="s">
-        <v>74</v>
+      <c r="A61">
+        <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>461</v>
+        <v>70</v>
       </c>
       <c r="C61">
         <v>1</v>
@@ -5471,11 +4439,11 @@
       </c>
     </row>
     <row r="62" spans="1:15">
-      <c r="A62" t="s">
-        <v>75</v>
+      <c r="A62">
+        <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>462</v>
+        <v>71</v>
       </c>
       <c r="C62">
         <v>1</v>
@@ -5518,11 +4486,11 @@
       </c>
     </row>
     <row r="63" spans="1:15">
-      <c r="A63" t="s">
-        <v>76</v>
+      <c r="A63">
+        <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>463</v>
+        <v>72</v>
       </c>
       <c r="C63">
         <v>1</v>
@@ -5565,11 +4533,11 @@
       </c>
     </row>
     <row r="64" spans="1:15">
-      <c r="A64" t="s">
-        <v>77</v>
+      <c r="A64">
+        <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>464</v>
+        <v>73</v>
       </c>
       <c r="C64">
         <v>1</v>
@@ -5612,11 +4580,11 @@
       </c>
     </row>
     <row r="65" spans="1:15">
-      <c r="A65" t="s">
-        <v>78</v>
+      <c r="A65">
+        <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>465</v>
+        <v>74</v>
       </c>
       <c r="C65">
         <v>1</v>
@@ -5659,11 +4627,11 @@
       </c>
     </row>
     <row r="66" spans="1:15">
-      <c r="A66" t="s">
-        <v>79</v>
+      <c r="A66">
+        <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>466</v>
+        <v>75</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -5706,11 +4674,11 @@
       </c>
     </row>
     <row r="67" spans="1:15">
-      <c r="A67" t="s">
-        <v>80</v>
+      <c r="A67">
+        <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>467</v>
+        <v>76</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -5753,11 +4721,11 @@
       </c>
     </row>
     <row r="68" spans="1:15">
-      <c r="A68" t="s">
-        <v>81</v>
+      <c r="A68">
+        <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>468</v>
+        <v>77</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -5800,11 +4768,11 @@
       </c>
     </row>
     <row r="69" spans="1:15">
-      <c r="A69" t="s">
-        <v>82</v>
+      <c r="A69">
+        <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>469</v>
+        <v>78</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -5847,11 +4815,11 @@
       </c>
     </row>
     <row r="70" spans="1:15">
-      <c r="A70" t="s">
-        <v>83</v>
+      <c r="A70">
+        <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>470</v>
+        <v>79</v>
       </c>
       <c r="C70">
         <v>1</v>
@@ -5894,11 +4862,11 @@
       </c>
     </row>
     <row r="71" spans="1:15">
-      <c r="A71" t="s">
-        <v>84</v>
+      <c r="A71">
+        <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>471</v>
+        <v>80</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -5941,11 +4909,11 @@
       </c>
     </row>
     <row r="72" spans="1:15">
-      <c r="A72" t="s">
-        <v>85</v>
+      <c r="A72">
+        <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>472</v>
+        <v>81</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -5988,11 +4956,11 @@
       </c>
     </row>
     <row r="73" spans="1:15">
-      <c r="A73" t="s">
-        <v>86</v>
+      <c r="A73">
+        <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>473</v>
+        <v>82</v>
       </c>
       <c r="C73">
         <v>1</v>
@@ -6035,11 +5003,11 @@
       </c>
     </row>
     <row r="74" spans="1:15">
-      <c r="A74" t="s">
-        <v>87</v>
+      <c r="A74">
+        <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>474</v>
+        <v>83</v>
       </c>
       <c r="C74">
         <v>1</v>
@@ -6082,11 +5050,11 @@
       </c>
     </row>
     <row r="75" spans="1:15">
-      <c r="A75" t="s">
-        <v>88</v>
+      <c r="A75">
+        <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>475</v>
+        <v>84</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -6129,11 +5097,11 @@
       </c>
     </row>
     <row r="76" spans="1:15">
-      <c r="A76" t="s">
-        <v>89</v>
+      <c r="A76">
+        <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>476</v>
+        <v>85</v>
       </c>
       <c r="C76">
         <v>1</v>
@@ -6176,11 +5144,11 @@
       </c>
     </row>
     <row r="77" spans="1:15">
-      <c r="A77" t="s">
-        <v>90</v>
+      <c r="A77">
+        <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>477</v>
+        <v>86</v>
       </c>
       <c r="C77">
         <v>1</v>
@@ -6223,11 +5191,11 @@
       </c>
     </row>
     <row r="78" spans="1:15">
-      <c r="A78" t="s">
-        <v>91</v>
+      <c r="A78">
+        <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>478</v>
+        <v>87</v>
       </c>
       <c r="C78">
         <v>1</v>
@@ -6270,11 +5238,11 @@
       </c>
     </row>
     <row r="79" spans="1:15">
-      <c r="A79" t="s">
-        <v>92</v>
+      <c r="A79">
+        <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>479</v>
+        <v>88</v>
       </c>
       <c r="C79">
         <v>1</v>
@@ -6317,11 +5285,11 @@
       </c>
     </row>
     <row r="80" spans="1:15">
-      <c r="A80" t="s">
-        <v>93</v>
+      <c r="A80">
+        <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>480</v>
+        <v>89</v>
       </c>
       <c r="C80">
         <v>1</v>
@@ -6364,11 +5332,11 @@
       </c>
     </row>
     <row r="81" spans="1:15">
-      <c r="A81" t="s">
-        <v>94</v>
+      <c r="A81">
+        <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>481</v>
+        <v>90</v>
       </c>
       <c r="C81">
         <v>1</v>
@@ -6411,11 +5379,11 @@
       </c>
     </row>
     <row r="82" spans="1:15">
-      <c r="A82" t="s">
-        <v>95</v>
+      <c r="A82">
+        <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>482</v>
+        <v>91</v>
       </c>
       <c r="C82">
         <v>1</v>
@@ -6458,11 +5426,11 @@
       </c>
     </row>
     <row r="83" spans="1:15">
-      <c r="A83" t="s">
-        <v>96</v>
+      <c r="A83">
+        <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>483</v>
+        <v>92</v>
       </c>
       <c r="C83">
         <v>1</v>
@@ -6505,11 +5473,11 @@
       </c>
     </row>
     <row r="84" spans="1:15">
-      <c r="A84" t="s">
-        <v>97</v>
+      <c r="A84">
+        <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>484</v>
+        <v>93</v>
       </c>
       <c r="C84">
         <v>1</v>
@@ -6552,11 +5520,11 @@
       </c>
     </row>
     <row r="85" spans="1:15">
-      <c r="A85" t="s">
-        <v>98</v>
+      <c r="A85">
+        <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>485</v>
+        <v>94</v>
       </c>
       <c r="C85">
         <v>1</v>
@@ -6599,11 +5567,11 @@
       </c>
     </row>
     <row r="86" spans="1:15">
-      <c r="A86" t="s">
-        <v>99</v>
+      <c r="A86">
+        <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>486</v>
+        <v>95</v>
       </c>
       <c r="C86">
         <v>1</v>
@@ -6646,11 +5614,11 @@
       </c>
     </row>
     <row r="87" spans="1:15">
-      <c r="A87" t="s">
-        <v>100</v>
+      <c r="A87">
+        <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>487</v>
+        <v>96</v>
       </c>
       <c r="C87">
         <v>1</v>
@@ -6693,11 +5661,11 @@
       </c>
     </row>
     <row r="88" spans="1:15">
-      <c r="A88" t="s">
-        <v>101</v>
+      <c r="A88">
+        <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>488</v>
+        <v>97</v>
       </c>
       <c r="C88">
         <v>1</v>
@@ -6740,11 +5708,11 @@
       </c>
     </row>
     <row r="89" spans="1:15">
-      <c r="A89" t="s">
-        <v>102</v>
+      <c r="A89">
+        <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>489</v>
+        <v>98</v>
       </c>
       <c r="C89">
         <v>1</v>
@@ -6787,11 +5755,11 @@
       </c>
     </row>
     <row r="90" spans="1:15">
-      <c r="A90" t="s">
-        <v>103</v>
+      <c r="A90">
+        <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>490</v>
+        <v>99</v>
       </c>
       <c r="C90">
         <v>1</v>
@@ -6834,11 +5802,11 @@
       </c>
     </row>
     <row r="91" spans="1:15">
-      <c r="A91" t="s">
-        <v>104</v>
+      <c r="A91">
+        <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>491</v>
+        <v>100</v>
       </c>
       <c r="C91">
         <v>1</v>
@@ -6881,11 +5849,11 @@
       </c>
     </row>
     <row r="92" spans="1:15">
-      <c r="A92" t="s">
-        <v>105</v>
+      <c r="A92">
+        <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>492</v>
+        <v>101</v>
       </c>
       <c r="C92">
         <v>1</v>
@@ -6928,11 +5896,11 @@
       </c>
     </row>
     <row r="93" spans="1:15">
-      <c r="A93" t="s">
-        <v>106</v>
+      <c r="A93">
+        <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>493</v>
+        <v>102</v>
       </c>
       <c r="C93">
         <v>1</v>
@@ -6975,11 +5943,11 @@
       </c>
     </row>
     <row r="94" spans="1:15">
-      <c r="A94" t="s">
-        <v>107</v>
+      <c r="A94">
+        <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>494</v>
+        <v>103</v>
       </c>
       <c r="C94">
         <v>1</v>
@@ -7022,11 +5990,11 @@
       </c>
     </row>
     <row r="95" spans="1:15">
-      <c r="A95" t="s">
-        <v>108</v>
+      <c r="A95">
+        <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>495</v>
+        <v>104</v>
       </c>
       <c r="C95">
         <v>1</v>
@@ -7069,11 +6037,11 @@
       </c>
     </row>
     <row r="96" spans="1:15">
-      <c r="A96" t="s">
-        <v>109</v>
+      <c r="A96">
+        <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>496</v>
+        <v>105</v>
       </c>
       <c r="C96">
         <v>1</v>
@@ -7116,11 +6084,11 @@
       </c>
     </row>
     <row r="97" spans="1:15">
-      <c r="A97" t="s">
-        <v>110</v>
+      <c r="A97">
+        <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>497</v>
+        <v>106</v>
       </c>
       <c r="C97">
         <v>1</v>
@@ -7163,11 +6131,11 @@
       </c>
     </row>
     <row r="98" spans="1:15">
-      <c r="A98" t="s">
-        <v>111</v>
+      <c r="A98">
+        <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>498</v>
+        <v>107</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -7210,11 +6178,11 @@
       </c>
     </row>
     <row r="99" spans="1:15">
-      <c r="A99" t="s">
-        <v>112</v>
+      <c r="A99">
+        <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>499</v>
+        <v>108</v>
       </c>
       <c r="C99">
         <v>1</v>
@@ -7257,11 +6225,11 @@
       </c>
     </row>
     <row r="100" spans="1:15">
-      <c r="A100" t="s">
-        <v>113</v>
+      <c r="A100">
+        <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>500</v>
+        <v>109</v>
       </c>
       <c r="C100">
         <v>1</v>
@@ -7304,11 +6272,11 @@
       </c>
     </row>
     <row r="101" spans="1:15">
-      <c r="A101" t="s">
-        <v>114</v>
+      <c r="A101">
+        <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>501</v>
+        <v>110</v>
       </c>
       <c r="C101">
         <v>1</v>
@@ -7351,11 +6319,11 @@
       </c>
     </row>
     <row r="102" spans="1:15">
-      <c r="A102" t="s">
-        <v>115</v>
+      <c r="A102">
+        <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>502</v>
+        <v>111</v>
       </c>
       <c r="C102">
         <v>1</v>
@@ -7398,11 +6366,11 @@
       </c>
     </row>
     <row r="103" spans="1:15">
-      <c r="A103" t="s">
-        <v>116</v>
+      <c r="A103">
+        <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>503</v>
+        <v>112</v>
       </c>
       <c r="C103">
         <v>1</v>
@@ -7445,11 +6413,11 @@
       </c>
     </row>
     <row r="104" spans="1:15">
-      <c r="A104" t="s">
-        <v>117</v>
+      <c r="A104">
+        <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>504</v>
+        <v>113</v>
       </c>
       <c r="C104">
         <v>1</v>
@@ -7492,11 +6460,11 @@
       </c>
     </row>
     <row r="105" spans="1:15">
-      <c r="A105" t="s">
-        <v>118</v>
+      <c r="A105">
+        <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>505</v>
+        <v>114</v>
       </c>
       <c r="C105">
         <v>1</v>
@@ -7539,11 +6507,11 @@
       </c>
     </row>
     <row r="106" spans="1:15">
-      <c r="A106" t="s">
-        <v>119</v>
+      <c r="A106">
+        <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>506</v>
+        <v>115</v>
       </c>
       <c r="C106">
         <v>1</v>
@@ -7586,11 +6554,11 @@
       </c>
     </row>
     <row r="107" spans="1:15">
-      <c r="A107" t="s">
-        <v>120</v>
+      <c r="A107">
+        <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>507</v>
+        <v>116</v>
       </c>
       <c r="C107">
         <v>1</v>
@@ -7633,11 +6601,11 @@
       </c>
     </row>
     <row r="108" spans="1:15">
-      <c r="A108" t="s">
-        <v>121</v>
+      <c r="A108">
+        <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>508</v>
+        <v>117</v>
       </c>
       <c r="C108">
         <v>1</v>
@@ -7680,11 +6648,11 @@
       </c>
     </row>
     <row r="109" spans="1:15">
-      <c r="A109" t="s">
-        <v>122</v>
+      <c r="A109">
+        <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>509</v>
+        <v>118</v>
       </c>
       <c r="C109">
         <v>1</v>
@@ -7727,11 +6695,11 @@
       </c>
     </row>
     <row r="110" spans="1:15">
-      <c r="A110" t="s">
-        <v>123</v>
+      <c r="A110">
+        <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>510</v>
+        <v>119</v>
       </c>
       <c r="C110">
         <v>1</v>
@@ -7774,11 +6742,11 @@
       </c>
     </row>
     <row r="111" spans="1:15">
-      <c r="A111" t="s">
-        <v>124</v>
+      <c r="A111">
+        <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>511</v>
+        <v>120</v>
       </c>
       <c r="C111">
         <v>1</v>
@@ -7821,11 +6789,11 @@
       </c>
     </row>
     <row r="112" spans="1:15">
-      <c r="A112" t="s">
-        <v>125</v>
+      <c r="A112">
+        <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>512</v>
+        <v>121</v>
       </c>
       <c r="C112">
         <v>1</v>
@@ -7868,11 +6836,11 @@
       </c>
     </row>
     <row r="113" spans="1:15">
-      <c r="A113" t="s">
-        <v>126</v>
+      <c r="A113">
+        <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>513</v>
+        <v>122</v>
       </c>
       <c r="C113">
         <v>1</v>
@@ -7915,11 +6883,11 @@
       </c>
     </row>
     <row r="114" spans="1:15">
-      <c r="A114" t="s">
-        <v>127</v>
+      <c r="A114">
+        <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>514</v>
+        <v>123</v>
       </c>
       <c r="C114">
         <v>1</v>
@@ -7962,11 +6930,11 @@
       </c>
     </row>
     <row r="115" spans="1:15">
-      <c r="A115" t="s">
-        <v>128</v>
+      <c r="A115">
+        <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>515</v>
+        <v>124</v>
       </c>
       <c r="C115">
         <v>1</v>
@@ -8009,11 +6977,11 @@
       </c>
     </row>
     <row r="116" spans="1:15">
-      <c r="A116" t="s">
-        <v>129</v>
+      <c r="A116">
+        <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>516</v>
+        <v>125</v>
       </c>
       <c r="C116">
         <v>1</v>
@@ -8056,11 +7024,11 @@
       </c>
     </row>
     <row r="117" spans="1:15">
-      <c r="A117" t="s">
-        <v>130</v>
+      <c r="A117">
+        <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>517</v>
+        <v>126</v>
       </c>
       <c r="C117">
         <v>1</v>
@@ -8103,11 +7071,11 @@
       </c>
     </row>
     <row r="118" spans="1:15">
-      <c r="A118" t="s">
-        <v>131</v>
+      <c r="A118">
+        <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>518</v>
+        <v>127</v>
       </c>
       <c r="C118">
         <v>1</v>
@@ -8150,11 +7118,11 @@
       </c>
     </row>
     <row r="119" spans="1:15">
-      <c r="A119" t="s">
-        <v>132</v>
+      <c r="A119">
+        <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>519</v>
+        <v>128</v>
       </c>
       <c r="C119">
         <v>1</v>
@@ -8197,11 +7165,11 @@
       </c>
     </row>
     <row r="120" spans="1:15">
-      <c r="A120" t="s">
-        <v>133</v>
+      <c r="A120">
+        <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>520</v>
+        <v>129</v>
       </c>
       <c r="C120">
         <v>1</v>
@@ -8244,11 +7212,11 @@
       </c>
     </row>
     <row r="121" spans="1:15">
-      <c r="A121" t="s">
-        <v>134</v>
+      <c r="A121">
+        <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>521</v>
+        <v>130</v>
       </c>
       <c r="C121">
         <v>1</v>
@@ -8291,11 +7259,11 @@
       </c>
     </row>
     <row r="122" spans="1:15">
-      <c r="A122" t="s">
-        <v>135</v>
+      <c r="A122">
+        <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>522</v>
+        <v>131</v>
       </c>
       <c r="C122">
         <v>1</v>
@@ -8338,11 +7306,11 @@
       </c>
     </row>
     <row r="123" spans="1:15">
-      <c r="A123" t="s">
-        <v>136</v>
+      <c r="A123">
+        <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>523</v>
+        <v>132</v>
       </c>
       <c r="C123">
         <v>1</v>
@@ -8385,11 +7353,11 @@
       </c>
     </row>
     <row r="124" spans="1:15">
-      <c r="A124" t="s">
-        <v>137</v>
+      <c r="A124">
+        <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>524</v>
+        <v>133</v>
       </c>
       <c r="C124">
         <v>1</v>
@@ -8432,11 +7400,11 @@
       </c>
     </row>
     <row r="125" spans="1:15">
-      <c r="A125" t="s">
-        <v>138</v>
+      <c r="A125">
+        <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>525</v>
+        <v>134</v>
       </c>
       <c r="C125">
         <v>1</v>
@@ -8479,11 +7447,11 @@
       </c>
     </row>
     <row r="126" spans="1:15">
-      <c r="A126" t="s">
-        <v>139</v>
+      <c r="A126">
+        <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>526</v>
+        <v>135</v>
       </c>
       <c r="C126">
         <v>1</v>
@@ -8526,11 +7494,11 @@
       </c>
     </row>
     <row r="127" spans="1:15">
-      <c r="A127" t="s">
-        <v>140</v>
+      <c r="A127">
+        <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>527</v>
+        <v>136</v>
       </c>
       <c r="C127">
         <v>1</v>
@@ -8573,11 +7541,11 @@
       </c>
     </row>
     <row r="128" spans="1:15">
-      <c r="A128" t="s">
-        <v>141</v>
+      <c r="A128">
+        <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>528</v>
+        <v>137</v>
       </c>
       <c r="C128">
         <v>1</v>
@@ -8620,11 +7588,11 @@
       </c>
     </row>
     <row r="129" spans="1:15">
-      <c r="A129" t="s">
-        <v>142</v>
+      <c r="A129">
+        <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>529</v>
+        <v>138</v>
       </c>
       <c r="C129">
         <v>1</v>
@@ -8667,11 +7635,11 @@
       </c>
     </row>
     <row r="130" spans="1:15">
-      <c r="A130" t="s">
-        <v>143</v>
+      <c r="A130">
+        <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>530</v>
+        <v>139</v>
       </c>
       <c r="C130">
         <v>1</v>
@@ -8714,11 +7682,11 @@
       </c>
     </row>
     <row r="131" spans="1:15">
-      <c r="A131" t="s">
-        <v>144</v>
+      <c r="A131">
+        <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>531</v>
+        <v>140</v>
       </c>
       <c r="C131">
         <v>1</v>
@@ -8761,11 +7729,11 @@
       </c>
     </row>
     <row r="132" spans="1:15">
-      <c r="A132" t="s">
-        <v>145</v>
+      <c r="A132">
+        <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>532</v>
+        <v>141</v>
       </c>
       <c r="C132">
         <v>1</v>
@@ -8808,11 +7776,11 @@
       </c>
     </row>
     <row r="133" spans="1:15">
-      <c r="A133" t="s">
-        <v>146</v>
+      <c r="A133">
+        <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>533</v>
+        <v>142</v>
       </c>
       <c r="C133">
         <v>1</v>
@@ -8855,11 +7823,11 @@
       </c>
     </row>
     <row r="134" spans="1:15">
-      <c r="A134" t="s">
-        <v>147</v>
+      <c r="A134">
+        <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>534</v>
+        <v>143</v>
       </c>
       <c r="C134">
         <v>1</v>
@@ -8902,11 +7870,11 @@
       </c>
     </row>
     <row r="135" spans="1:15">
-      <c r="A135" t="s">
-        <v>148</v>
+      <c r="A135">
+        <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>535</v>
+        <v>144</v>
       </c>
       <c r="C135">
         <v>1</v>
@@ -8949,11 +7917,11 @@
       </c>
     </row>
     <row r="136" spans="1:15">
-      <c r="A136" t="s">
-        <v>149</v>
+      <c r="A136">
+        <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>536</v>
+        <v>145</v>
       </c>
       <c r="C136">
         <v>1</v>
@@ -8996,11 +7964,11 @@
       </c>
     </row>
     <row r="137" spans="1:15">
-      <c r="A137" t="s">
-        <v>150</v>
+      <c r="A137">
+        <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>537</v>
+        <v>146</v>
       </c>
       <c r="C137">
         <v>1</v>
@@ -9043,11 +8011,11 @@
       </c>
     </row>
     <row r="138" spans="1:15">
-      <c r="A138" t="s">
-        <v>151</v>
+      <c r="A138">
+        <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>538</v>
+        <v>147</v>
       </c>
       <c r="C138">
         <v>1</v>
@@ -9090,11 +8058,11 @@
       </c>
     </row>
     <row r="139" spans="1:15">
-      <c r="A139" t="s">
-        <v>152</v>
+      <c r="A139">
+        <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>539</v>
+        <v>148</v>
       </c>
       <c r="C139">
         <v>1</v>
@@ -9137,11 +8105,11 @@
       </c>
     </row>
     <row r="140" spans="1:15">
-      <c r="A140" t="s">
-        <v>153</v>
+      <c r="A140">
+        <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>540</v>
+        <v>149</v>
       </c>
       <c r="C140">
         <v>1</v>
@@ -9184,11 +8152,11 @@
       </c>
     </row>
     <row r="141" spans="1:15">
-      <c r="A141" t="s">
-        <v>154</v>
+      <c r="A141">
+        <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>541</v>
+        <v>150</v>
       </c>
       <c r="C141">
         <v>1</v>
@@ -9231,11 +8199,11 @@
       </c>
     </row>
     <row r="142" spans="1:15">
-      <c r="A142" t="s">
-        <v>155</v>
+      <c r="A142">
+        <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>542</v>
+        <v>151</v>
       </c>
       <c r="C142">
         <v>1</v>
@@ -9278,11 +8246,11 @@
       </c>
     </row>
     <row r="143" spans="1:15">
-      <c r="A143" t="s">
-        <v>156</v>
+      <c r="A143">
+        <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>543</v>
+        <v>152</v>
       </c>
       <c r="C143">
         <v>1</v>
@@ -9325,11 +8293,11 @@
       </c>
     </row>
     <row r="144" spans="1:15">
-      <c r="A144" t="s">
-        <v>157</v>
+      <c r="A144">
+        <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>544</v>
+        <v>153</v>
       </c>
       <c r="C144">
         <v>1</v>
@@ -9372,11 +8340,11 @@
       </c>
     </row>
     <row r="145" spans="1:15">
-      <c r="A145" t="s">
-        <v>158</v>
+      <c r="A145">
+        <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>545</v>
+        <v>154</v>
       </c>
       <c r="C145">
         <v>1</v>
@@ -9419,11 +8387,11 @@
       </c>
     </row>
     <row r="146" spans="1:15">
-      <c r="A146" t="s">
-        <v>159</v>
+      <c r="A146">
+        <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>546</v>
+        <v>155</v>
       </c>
       <c r="C146">
         <v>1</v>
@@ -9466,11 +8434,11 @@
       </c>
     </row>
     <row r="147" spans="1:15">
-      <c r="A147" t="s">
-        <v>160</v>
+      <c r="A147">
+        <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>547</v>
+        <v>156</v>
       </c>
       <c r="C147">
         <v>1</v>
@@ -9513,11 +8481,11 @@
       </c>
     </row>
     <row r="148" spans="1:15">
-      <c r="A148" t="s">
-        <v>161</v>
+      <c r="A148">
+        <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>548</v>
+        <v>157</v>
       </c>
       <c r="C148">
         <v>1</v>
@@ -9560,11 +8528,11 @@
       </c>
     </row>
     <row r="149" spans="1:15">
-      <c r="A149" t="s">
-        <v>162</v>
+      <c r="A149">
+        <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>549</v>
+        <v>158</v>
       </c>
       <c r="C149">
         <v>1</v>
@@ -9607,11 +8575,11 @@
       </c>
     </row>
     <row r="150" spans="1:15">
-      <c r="A150" t="s">
-        <v>163</v>
+      <c r="A150">
+        <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>550</v>
+        <v>159</v>
       </c>
       <c r="C150">
         <v>1</v>
@@ -9654,11 +8622,11 @@
       </c>
     </row>
     <row r="151" spans="1:15">
-      <c r="A151" t="s">
-        <v>164</v>
+      <c r="A151">
+        <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>551</v>
+        <v>160</v>
       </c>
       <c r="C151">
         <v>1</v>
@@ -9701,11 +8669,11 @@
       </c>
     </row>
     <row r="152" spans="1:15">
-      <c r="A152" t="s">
-        <v>165</v>
+      <c r="A152">
+        <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>552</v>
+        <v>161</v>
       </c>
       <c r="C152">
         <v>1</v>
@@ -9748,11 +8716,11 @@
       </c>
     </row>
     <row r="153" spans="1:15">
-      <c r="A153" t="s">
-        <v>166</v>
+      <c r="A153">
+        <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>553</v>
+        <v>162</v>
       </c>
       <c r="C153">
         <v>1</v>
@@ -9795,11 +8763,11 @@
       </c>
     </row>
     <row r="154" spans="1:15">
-      <c r="A154" t="s">
-        <v>167</v>
+      <c r="A154">
+        <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>554</v>
+        <v>163</v>
       </c>
       <c r="C154">
         <v>1</v>
@@ -9842,11 +8810,11 @@
       </c>
     </row>
     <row r="155" spans="1:15">
-      <c r="A155" t="s">
-        <v>168</v>
+      <c r="A155">
+        <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>528</v>
+        <v>137</v>
       </c>
       <c r="C155">
         <v>1</v>
@@ -9889,11 +8857,11 @@
       </c>
     </row>
     <row r="156" spans="1:15">
-      <c r="A156" t="s">
-        <v>169</v>
+      <c r="A156">
+        <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>555</v>
+        <v>164</v>
       </c>
       <c r="C156">
         <v>1</v>
@@ -9936,11 +8904,11 @@
       </c>
     </row>
     <row r="157" spans="1:15">
-      <c r="A157" t="s">
-        <v>170</v>
+      <c r="A157">
+        <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>556</v>
+        <v>165</v>
       </c>
       <c r="C157">
         <v>1</v>
@@ -9983,11 +8951,11 @@
       </c>
     </row>
     <row r="158" spans="1:15">
-      <c r="A158" t="s">
-        <v>171</v>
+      <c r="A158">
+        <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>557</v>
+        <v>166</v>
       </c>
       <c r="C158">
         <v>1</v>
@@ -10030,11 +8998,11 @@
       </c>
     </row>
     <row r="159" spans="1:15">
-      <c r="A159" t="s">
-        <v>172</v>
+      <c r="A159">
+        <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>558</v>
+        <v>167</v>
       </c>
       <c r="C159">
         <v>1</v>
@@ -10077,11 +9045,11 @@
       </c>
     </row>
     <row r="160" spans="1:15">
-      <c r="A160" t="s">
-        <v>173</v>
+      <c r="A160">
+        <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>559</v>
+        <v>168</v>
       </c>
       <c r="C160">
         <v>1</v>
@@ -10124,11 +9092,11 @@
       </c>
     </row>
     <row r="161" spans="1:15">
-      <c r="A161" t="s">
-        <v>174</v>
+      <c r="A161">
+        <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>560</v>
+        <v>169</v>
       </c>
       <c r="C161">
         <v>1</v>
@@ -10171,11 +9139,11 @@
       </c>
     </row>
     <row r="162" spans="1:15">
-      <c r="A162" t="s">
-        <v>175</v>
+      <c r="A162">
+        <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>561</v>
+        <v>170</v>
       </c>
       <c r="C162">
         <v>1</v>
@@ -10218,11 +9186,11 @@
       </c>
     </row>
     <row r="163" spans="1:15">
-      <c r="A163" t="s">
-        <v>176</v>
+      <c r="A163">
+        <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>562</v>
+        <v>171</v>
       </c>
       <c r="C163">
         <v>1</v>
@@ -10265,11 +9233,11 @@
       </c>
     </row>
     <row r="164" spans="1:15">
-      <c r="A164" t="s">
-        <v>177</v>
+      <c r="A164">
+        <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>563</v>
+        <v>172</v>
       </c>
       <c r="C164">
         <v>1</v>
@@ -10312,11 +9280,11 @@
       </c>
     </row>
     <row r="165" spans="1:15">
-      <c r="A165" t="s">
-        <v>178</v>
+      <c r="A165">
+        <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>564</v>
+        <v>173</v>
       </c>
       <c r="C165">
         <v>1</v>
@@ -10359,11 +9327,11 @@
       </c>
     </row>
     <row r="166" spans="1:15">
-      <c r="A166" t="s">
-        <v>179</v>
+      <c r="A166">
+        <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>565</v>
+        <v>174</v>
       </c>
       <c r="C166">
         <v>1</v>
@@ -10406,11 +9374,11 @@
       </c>
     </row>
     <row r="167" spans="1:15">
-      <c r="A167" t="s">
-        <v>180</v>
+      <c r="A167">
+        <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>566</v>
+        <v>175</v>
       </c>
       <c r="C167">
         <v>1</v>
@@ -10453,11 +9421,11 @@
       </c>
     </row>
     <row r="168" spans="1:15">
-      <c r="A168" t="s">
-        <v>181</v>
+      <c r="A168">
+        <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>567</v>
+        <v>176</v>
       </c>
       <c r="C168">
         <v>1</v>
@@ -10500,11 +9468,11 @@
       </c>
     </row>
     <row r="169" spans="1:15">
-      <c r="A169" t="s">
-        <v>182</v>
+      <c r="A169">
+        <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>568</v>
+        <v>177</v>
       </c>
       <c r="C169">
         <v>1</v>
@@ -10547,11 +9515,11 @@
       </c>
     </row>
     <row r="170" spans="1:15">
-      <c r="A170" t="s">
-        <v>183</v>
+      <c r="A170">
+        <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>569</v>
+        <v>178</v>
       </c>
       <c r="C170">
         <v>1</v>
@@ -10594,11 +9562,11 @@
       </c>
     </row>
     <row r="171" spans="1:15">
-      <c r="A171" t="s">
-        <v>184</v>
+      <c r="A171">
+        <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>570</v>
+        <v>179</v>
       </c>
       <c r="C171">
         <v>1</v>
@@ -10641,11 +9609,11 @@
       </c>
     </row>
     <row r="172" spans="1:15">
-      <c r="A172" t="s">
-        <v>185</v>
+      <c r="A172">
+        <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>571</v>
+        <v>180</v>
       </c>
       <c r="C172">
         <v>1</v>
@@ -10688,11 +9656,11 @@
       </c>
     </row>
     <row r="173" spans="1:15">
-      <c r="A173" t="s">
-        <v>186</v>
+      <c r="A173">
+        <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>572</v>
+        <v>181</v>
       </c>
       <c r="C173">
         <v>1</v>
@@ -10735,11 +9703,11 @@
       </c>
     </row>
     <row r="174" spans="1:15">
-      <c r="A174" t="s">
-        <v>187</v>
+      <c r="A174">
+        <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>573</v>
+        <v>182</v>
       </c>
       <c r="C174">
         <v>1</v>
@@ -10782,11 +9750,11 @@
       </c>
     </row>
     <row r="175" spans="1:15">
-      <c r="A175" t="s">
-        <v>188</v>
+      <c r="A175">
+        <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>574</v>
+        <v>183</v>
       </c>
       <c r="C175">
         <v>1</v>
@@ -10829,11 +9797,11 @@
       </c>
     </row>
     <row r="176" spans="1:15">
-      <c r="A176" t="s">
-        <v>189</v>
+      <c r="A176">
+        <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>575</v>
+        <v>184</v>
       </c>
       <c r="C176">
         <v>1</v>
@@ -10876,11 +9844,11 @@
       </c>
     </row>
     <row r="177" spans="1:15">
-      <c r="A177" t="s">
-        <v>190</v>
+      <c r="A177">
+        <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>575</v>
+        <v>184</v>
       </c>
       <c r="C177">
         <v>1</v>
@@ -10923,11 +9891,11 @@
       </c>
     </row>
     <row r="178" spans="1:15">
-      <c r="A178" t="s">
-        <v>191</v>
+      <c r="A178">
+        <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>576</v>
+        <v>185</v>
       </c>
       <c r="C178">
         <v>1</v>
@@ -10970,11 +9938,11 @@
       </c>
     </row>
     <row r="179" spans="1:15">
-      <c r="A179" t="s">
-        <v>192</v>
+      <c r="A179">
+        <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>577</v>
+        <v>186</v>
       </c>
       <c r="C179">
         <v>1</v>
@@ -11017,11 +9985,11 @@
       </c>
     </row>
     <row r="180" spans="1:15">
-      <c r="A180" t="s">
-        <v>193</v>
+      <c r="A180">
+        <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>578</v>
+        <v>187</v>
       </c>
       <c r="C180">
         <v>1</v>
@@ -11064,11 +10032,11 @@
       </c>
     </row>
     <row r="181" spans="1:15">
-      <c r="A181" t="s">
-        <v>194</v>
+      <c r="A181">
+        <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>579</v>
+        <v>188</v>
       </c>
       <c r="C181">
         <v>1</v>
@@ -11111,11 +10079,11 @@
       </c>
     </row>
     <row r="182" spans="1:15">
-      <c r="A182" t="s">
-        <v>195</v>
+      <c r="A182">
+        <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>580</v>
+        <v>189</v>
       </c>
       <c r="C182">
         <v>1</v>
@@ -11158,11 +10126,11 @@
       </c>
     </row>
     <row r="183" spans="1:15">
-      <c r="A183" t="s">
-        <v>196</v>
+      <c r="A183">
+        <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>581</v>
+        <v>190</v>
       </c>
       <c r="C183">
         <v>1</v>
@@ -11205,11 +10173,11 @@
       </c>
     </row>
     <row r="184" spans="1:15">
-      <c r="A184" t="s">
-        <v>197</v>
+      <c r="A184">
+        <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>582</v>
+        <v>191</v>
       </c>
       <c r="C184">
         <v>1</v>
@@ -11252,11 +10220,11 @@
       </c>
     </row>
     <row r="185" spans="1:15">
-      <c r="A185" t="s">
-        <v>198</v>
+      <c r="A185">
+        <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>583</v>
+        <v>192</v>
       </c>
       <c r="C185">
         <v>1</v>
@@ -11299,11 +10267,11 @@
       </c>
     </row>
     <row r="186" spans="1:15">
-      <c r="A186" t="s">
-        <v>199</v>
+      <c r="A186">
+        <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>584</v>
+        <v>193</v>
       </c>
       <c r="C186">
         <v>1</v>
@@ -11346,11 +10314,11 @@
       </c>
     </row>
     <row r="187" spans="1:15">
-      <c r="A187" t="s">
-        <v>200</v>
+      <c r="A187">
+        <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>585</v>
+        <v>194</v>
       </c>
       <c r="C187">
         <v>1</v>
@@ -11393,11 +10361,11 @@
       </c>
     </row>
     <row r="188" spans="1:15">
-      <c r="A188" t="s">
-        <v>201</v>
+      <c r="A188">
+        <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>586</v>
+        <v>195</v>
       </c>
       <c r="C188">
         <v>1</v>
@@ -11440,11 +10408,11 @@
       </c>
     </row>
     <row r="189" spans="1:15">
-      <c r="A189" t="s">
-        <v>202</v>
+      <c r="A189">
+        <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>587</v>
+        <v>196</v>
       </c>
       <c r="C189">
         <v>1</v>
@@ -11487,11 +10455,11 @@
       </c>
     </row>
     <row r="190" spans="1:15">
-      <c r="A190" t="s">
-        <v>203</v>
+      <c r="A190">
+        <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>588</v>
+        <v>197</v>
       </c>
       <c r="C190">
         <v>1</v>
@@ -11534,11 +10502,11 @@
       </c>
     </row>
     <row r="191" spans="1:15">
-      <c r="A191" t="s">
-        <v>204</v>
+      <c r="A191">
+        <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>589</v>
+        <v>198</v>
       </c>
       <c r="C191">
         <v>1</v>
@@ -11581,11 +10549,11 @@
       </c>
     </row>
     <row r="192" spans="1:15">
-      <c r="A192" t="s">
-        <v>205</v>
+      <c r="A192">
+        <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>590</v>
+        <v>199</v>
       </c>
       <c r="C192">
         <v>1</v>
@@ -11628,11 +10596,11 @@
       </c>
     </row>
     <row r="193" spans="1:15">
-      <c r="A193" t="s">
-        <v>206</v>
+      <c r="A193">
+        <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>591</v>
+        <v>200</v>
       </c>
       <c r="C193">
         <v>1</v>
@@ -11675,11 +10643,11 @@
       </c>
     </row>
     <row r="194" spans="1:15">
-      <c r="A194" t="s">
-        <v>207</v>
+      <c r="A194">
+        <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>592</v>
+        <v>201</v>
       </c>
       <c r="C194">
         <v>1</v>
@@ -11722,11 +10690,11 @@
       </c>
     </row>
     <row r="195" spans="1:15">
-      <c r="A195" t="s">
-        <v>208</v>
+      <c r="A195">
+        <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>593</v>
+        <v>202</v>
       </c>
       <c r="C195">
         <v>1</v>
@@ -11769,11 +10737,11 @@
       </c>
     </row>
     <row r="196" spans="1:15">
-      <c r="A196" t="s">
-        <v>209</v>
+      <c r="A196">
+        <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>594</v>
+        <v>203</v>
       </c>
       <c r="C196">
         <v>1</v>
@@ -11816,11 +10784,11 @@
       </c>
     </row>
     <row r="197" spans="1:15">
-      <c r="A197" t="s">
-        <v>210</v>
+      <c r="A197">
+        <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>595</v>
+        <v>204</v>
       </c>
       <c r="C197">
         <v>1</v>
@@ -11863,11 +10831,11 @@
       </c>
     </row>
     <row r="198" spans="1:15">
-      <c r="A198" t="s">
-        <v>211</v>
+      <c r="A198">
+        <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>596</v>
+        <v>205</v>
       </c>
       <c r="C198">
         <v>1</v>
@@ -11910,11 +10878,11 @@
       </c>
     </row>
     <row r="199" spans="1:15">
-      <c r="A199" t="s">
-        <v>212</v>
+      <c r="A199">
+        <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>596</v>
+        <v>205</v>
       </c>
       <c r="C199">
         <v>1</v>
@@ -11957,11 +10925,11 @@
       </c>
     </row>
     <row r="200" spans="1:15">
-      <c r="A200" t="s">
-        <v>213</v>
+      <c r="A200">
+        <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>597</v>
+        <v>206</v>
       </c>
       <c r="C200">
         <v>1</v>
@@ -12004,11 +10972,11 @@
       </c>
     </row>
     <row r="201" spans="1:15">
-      <c r="A201" t="s">
-        <v>214</v>
+      <c r="A201">
+        <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>598</v>
+        <v>207</v>
       </c>
       <c r="C201">
         <v>1</v>
@@ -12051,11 +11019,11 @@
       </c>
     </row>
     <row r="202" spans="1:15">
-      <c r="A202" t="s">
-        <v>215</v>
+      <c r="A202">
+        <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>599</v>
+        <v>208</v>
       </c>
       <c r="C202">
         <v>1</v>
@@ -12098,11 +11066,11 @@
       </c>
     </row>
     <row r="203" spans="1:15">
-      <c r="A203" t="s">
-        <v>216</v>
+      <c r="A203">
+        <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>600</v>
+        <v>209</v>
       </c>
       <c r="C203">
         <v>1</v>
@@ -12145,11 +11113,11 @@
       </c>
     </row>
     <row r="204" spans="1:15">
-      <c r="A204" t="s">
-        <v>217</v>
+      <c r="A204">
+        <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>601</v>
+        <v>210</v>
       </c>
       <c r="C204">
         <v>1</v>
@@ -12192,11 +11160,11 @@
       </c>
     </row>
     <row r="205" spans="1:15">
-      <c r="A205" t="s">
-        <v>218</v>
+      <c r="A205">
+        <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>602</v>
+        <v>211</v>
       </c>
       <c r="C205">
         <v>1</v>
@@ -12239,11 +11207,11 @@
       </c>
     </row>
     <row r="206" spans="1:15">
-      <c r="A206" t="s">
-        <v>219</v>
+      <c r="A206">
+        <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>603</v>
+        <v>212</v>
       </c>
       <c r="C206">
         <v>1</v>
@@ -12286,11 +11254,11 @@
       </c>
     </row>
     <row r="207" spans="1:15">
-      <c r="A207" t="s">
-        <v>220</v>
+      <c r="A207">
+        <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>604</v>
+        <v>213</v>
       </c>
       <c r="C207">
         <v>1</v>
@@ -12333,11 +11301,11 @@
       </c>
     </row>
     <row r="208" spans="1:15">
-      <c r="A208" t="s">
-        <v>221</v>
+      <c r="A208">
+        <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>605</v>
+        <v>214</v>
       </c>
       <c r="C208">
         <v>1</v>
@@ -12380,11 +11348,11 @@
       </c>
     </row>
     <row r="209" spans="1:15">
-      <c r="A209" t="s">
-        <v>222</v>
+      <c r="A209">
+        <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>606</v>
+        <v>215</v>
       </c>
       <c r="C209">
         <v>1</v>
@@ -12427,11 +11395,11 @@
       </c>
     </row>
     <row r="210" spans="1:15">
-      <c r="A210" t="s">
-        <v>223</v>
+      <c r="A210">
+        <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>607</v>
+        <v>216</v>
       </c>
       <c r="C210">
         <v>1</v>
@@ -12474,11 +11442,11 @@
       </c>
     </row>
     <row r="211" spans="1:15">
-      <c r="A211" t="s">
-        <v>224</v>
+      <c r="A211">
+        <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>607</v>
+        <v>216</v>
       </c>
       <c r="C211">
         <v>1</v>
@@ -12521,11 +11489,11 @@
       </c>
     </row>
     <row r="212" spans="1:15">
-      <c r="A212" t="s">
-        <v>225</v>
+      <c r="A212">
+        <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>608</v>
+        <v>217</v>
       </c>
       <c r="C212">
         <v>1</v>
@@ -12568,11 +11536,11 @@
       </c>
     </row>
     <row r="213" spans="1:15">
-      <c r="A213" t="s">
-        <v>226</v>
+      <c r="A213">
+        <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>609</v>
+        <v>218</v>
       </c>
       <c r="C213">
         <v>1</v>
@@ -12615,11 +11583,11 @@
       </c>
     </row>
     <row r="214" spans="1:15">
-      <c r="A214" t="s">
-        <v>227</v>
+      <c r="A214">
+        <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>610</v>
+        <v>219</v>
       </c>
       <c r="C214">
         <v>1</v>
@@ -12662,11 +11630,11 @@
       </c>
     </row>
     <row r="215" spans="1:15">
-      <c r="A215" t="s">
-        <v>228</v>
+      <c r="A215">
+        <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>611</v>
+        <v>220</v>
       </c>
       <c r="C215">
         <v>1</v>
@@ -12709,11 +11677,11 @@
       </c>
     </row>
     <row r="216" spans="1:15">
-      <c r="A216" t="s">
-        <v>229</v>
+      <c r="A216">
+        <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>612</v>
+        <v>221</v>
       </c>
       <c r="C216">
         <v>1</v>
@@ -12756,11 +11724,11 @@
       </c>
     </row>
     <row r="217" spans="1:15">
-      <c r="A217" t="s">
-        <v>230</v>
+      <c r="A217">
+        <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>613</v>
+        <v>222</v>
       </c>
       <c r="C217">
         <v>1</v>
@@ -12803,11 +11771,11 @@
       </c>
     </row>
     <row r="218" spans="1:15">
-      <c r="A218" t="s">
-        <v>231</v>
+      <c r="A218">
+        <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>614</v>
+        <v>223</v>
       </c>
       <c r="C218">
         <v>1</v>
@@ -12850,11 +11818,11 @@
       </c>
     </row>
     <row r="219" spans="1:15">
-      <c r="A219" t="s">
-        <v>232</v>
+      <c r="A219">
+        <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>615</v>
+        <v>224</v>
       </c>
       <c r="C219">
         <v>1</v>
@@ -12897,11 +11865,11 @@
       </c>
     </row>
     <row r="220" spans="1:15">
-      <c r="A220" t="s">
-        <v>233</v>
+      <c r="A220">
+        <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>616</v>
+        <v>225</v>
       </c>
       <c r="C220">
         <v>1</v>
@@ -12944,11 +11912,11 @@
       </c>
     </row>
     <row r="221" spans="1:15">
-      <c r="A221" t="s">
-        <v>234</v>
+      <c r="A221">
+        <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>617</v>
+        <v>226</v>
       </c>
       <c r="C221">
         <v>1</v>
@@ -12991,11 +11959,11 @@
       </c>
     </row>
     <row r="222" spans="1:15">
-      <c r="A222" t="s">
-        <v>235</v>
+      <c r="A222">
+        <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>618</v>
+        <v>227</v>
       </c>
       <c r="C222">
         <v>1</v>
@@ -13038,11 +12006,11 @@
       </c>
     </row>
     <row r="223" spans="1:15">
-      <c r="A223" t="s">
-        <v>236</v>
+      <c r="A223">
+        <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>619</v>
+        <v>228</v>
       </c>
       <c r="C223">
         <v>1</v>
@@ -13085,11 +12053,11 @@
       </c>
     </row>
     <row r="224" spans="1:15">
-      <c r="A224" t="s">
-        <v>237</v>
+      <c r="A224">
+        <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>620</v>
+        <v>229</v>
       </c>
       <c r="C224">
         <v>1</v>
@@ -13132,11 +12100,11 @@
       </c>
     </row>
     <row r="225" spans="1:15">
-      <c r="A225" t="s">
-        <v>238</v>
+      <c r="A225">
+        <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>621</v>
+        <v>230</v>
       </c>
       <c r="C225">
         <v>1</v>
@@ -13179,11 +12147,11 @@
       </c>
     </row>
     <row r="226" spans="1:15">
-      <c r="A226" t="s">
-        <v>239</v>
+      <c r="A226">
+        <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>622</v>
+        <v>231</v>
       </c>
       <c r="C226">
         <v>1</v>
@@ -13226,11 +12194,11 @@
       </c>
     </row>
     <row r="227" spans="1:15">
-      <c r="A227" t="s">
-        <v>240</v>
+      <c r="A227">
+        <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>623</v>
+        <v>232</v>
       </c>
       <c r="C227">
         <v>1</v>
@@ -13273,11 +12241,11 @@
       </c>
     </row>
     <row r="228" spans="1:15">
-      <c r="A228" t="s">
-        <v>241</v>
+      <c r="A228">
+        <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>624</v>
+        <v>233</v>
       </c>
       <c r="C228">
         <v>1</v>
@@ -13320,11 +12288,11 @@
       </c>
     </row>
     <row r="229" spans="1:15">
-      <c r="A229" t="s">
-        <v>242</v>
+      <c r="A229">
+        <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>625</v>
+        <v>234</v>
       </c>
       <c r="C229">
         <v>1</v>
@@ -13367,11 +12335,11 @@
       </c>
     </row>
     <row r="230" spans="1:15">
-      <c r="A230" t="s">
-        <v>243</v>
+      <c r="A230">
+        <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>626</v>
+        <v>235</v>
       </c>
       <c r="C230">
         <v>1</v>
@@ -13414,11 +12382,11 @@
       </c>
     </row>
     <row r="231" spans="1:15">
-      <c r="A231" t="s">
-        <v>244</v>
+      <c r="A231">
+        <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>627</v>
+        <v>236</v>
       </c>
       <c r="C231">
         <v>1</v>
@@ -13461,11 +12429,11 @@
       </c>
     </row>
     <row r="232" spans="1:15">
-      <c r="A232" t="s">
-        <v>245</v>
+      <c r="A232">
+        <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>628</v>
+        <v>237</v>
       </c>
       <c r="C232">
         <v>1</v>
@@ -13508,11 +12476,11 @@
       </c>
     </row>
     <row r="233" spans="1:15">
-      <c r="A233" t="s">
-        <v>246</v>
+      <c r="A233">
+        <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>629</v>
+        <v>238</v>
       </c>
       <c r="C233">
         <v>1</v>
@@ -13555,11 +12523,11 @@
       </c>
     </row>
     <row r="234" spans="1:15">
-      <c r="A234" t="s">
-        <v>247</v>
+      <c r="A234">
+        <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>630</v>
+        <v>239</v>
       </c>
       <c r="C234">
         <v>1</v>
@@ -13602,11 +12570,11 @@
       </c>
     </row>
     <row r="235" spans="1:15">
-      <c r="A235" t="s">
-        <v>248</v>
+      <c r="A235">
+        <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>631</v>
+        <v>240</v>
       </c>
       <c r="C235">
         <v>1</v>
@@ -13649,11 +12617,11 @@
       </c>
     </row>
     <row r="236" spans="1:15">
-      <c r="A236" t="s">
-        <v>249</v>
+      <c r="A236">
+        <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>632</v>
+        <v>241</v>
       </c>
       <c r="C236">
         <v>1</v>
@@ -13696,11 +12664,11 @@
       </c>
     </row>
     <row r="237" spans="1:15">
-      <c r="A237" t="s">
-        <v>250</v>
+      <c r="A237">
+        <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>633</v>
+        <v>242</v>
       </c>
       <c r="C237">
         <v>1</v>
@@ -13743,11 +12711,11 @@
       </c>
     </row>
     <row r="238" spans="1:15">
-      <c r="A238" t="s">
-        <v>251</v>
+      <c r="A238">
+        <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>634</v>
+        <v>243</v>
       </c>
       <c r="C238">
         <v>1</v>
@@ -13790,11 +12758,11 @@
       </c>
     </row>
     <row r="239" spans="1:15">
-      <c r="A239" t="s">
-        <v>252</v>
+      <c r="A239">
+        <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>635</v>
+        <v>244</v>
       </c>
       <c r="C239">
         <v>1</v>
@@ -13837,11 +12805,11 @@
       </c>
     </row>
     <row r="240" spans="1:15">
-      <c r="A240" t="s">
-        <v>253</v>
+      <c r="A240">
+        <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>636</v>
+        <v>245</v>
       </c>
       <c r="C240">
         <v>1</v>
@@ -13884,11 +12852,11 @@
       </c>
     </row>
     <row r="241" spans="1:15">
-      <c r="A241" t="s">
-        <v>254</v>
+      <c r="A241">
+        <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>637</v>
+        <v>246</v>
       </c>
       <c r="C241">
         <v>1</v>
@@ -13931,11 +12899,11 @@
       </c>
     </row>
     <row r="242" spans="1:15">
-      <c r="A242" t="s">
-        <v>255</v>
+      <c r="A242">
+        <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>638</v>
+        <v>247</v>
       </c>
       <c r="C242">
         <v>1</v>
@@ -13978,11 +12946,11 @@
       </c>
     </row>
     <row r="243" spans="1:15">
-      <c r="A243" t="s">
-        <v>256</v>
+      <c r="A243">
+        <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>639</v>
+        <v>248</v>
       </c>
       <c r="C243">
         <v>1</v>
@@ -14025,11 +12993,11 @@
       </c>
     </row>
     <row r="244" spans="1:15">
-      <c r="A244" t="s">
-        <v>257</v>
+      <c r="A244">
+        <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>640</v>
+        <v>249</v>
       </c>
       <c r="C244">
         <v>1</v>
@@ -14072,11 +13040,11 @@
       </c>
     </row>
     <row r="245" spans="1:15">
-      <c r="A245" t="s">
-        <v>258</v>
+      <c r="A245">
+        <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>641</v>
+        <v>250</v>
       </c>
       <c r="C245">
         <v>1</v>
@@ -14119,11 +13087,11 @@
       </c>
     </row>
     <row r="246" spans="1:15">
-      <c r="A246" t="s">
-        <v>259</v>
+      <c r="A246">
+        <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>642</v>
+        <v>251</v>
       </c>
       <c r="C246">
         <v>1</v>
@@ -14166,11 +13134,11 @@
       </c>
     </row>
     <row r="247" spans="1:15">
-      <c r="A247" t="s">
-        <v>260</v>
+      <c r="A247">
+        <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>643</v>
+        <v>252</v>
       </c>
       <c r="C247">
         <v>1</v>
@@ -14213,11 +13181,11 @@
       </c>
     </row>
     <row r="248" spans="1:15">
-      <c r="A248" t="s">
-        <v>261</v>
+      <c r="A248">
+        <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>644</v>
+        <v>253</v>
       </c>
       <c r="C248">
         <v>1</v>
@@ -14260,11 +13228,11 @@
       </c>
     </row>
     <row r="249" spans="1:15">
-      <c r="A249" t="s">
-        <v>262</v>
+      <c r="A249">
+        <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>645</v>
+        <v>254</v>
       </c>
       <c r="C249">
         <v>1</v>
@@ -14307,11 +13275,11 @@
       </c>
     </row>
     <row r="250" spans="1:15">
-      <c r="A250" t="s">
-        <v>263</v>
+      <c r="A250">
+        <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>646</v>
+        <v>255</v>
       </c>
       <c r="C250">
         <v>1</v>
@@ -14354,11 +13322,11 @@
       </c>
     </row>
     <row r="251" spans="1:15">
-      <c r="A251" t="s">
-        <v>264</v>
+      <c r="A251">
+        <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>647</v>
+        <v>256</v>
       </c>
       <c r="C251">
         <v>1</v>
@@ -14401,11 +13369,11 @@
       </c>
     </row>
     <row r="252" spans="1:15">
-      <c r="A252" t="s">
-        <v>265</v>
+      <c r="A252">
+        <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>648</v>
+        <v>257</v>
       </c>
       <c r="C252">
         <v>1</v>
@@ -14448,11 +13416,11 @@
       </c>
     </row>
     <row r="253" spans="1:15">
-      <c r="A253" t="s">
-        <v>266</v>
+      <c r="A253">
+        <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>649</v>
+        <v>258</v>
       </c>
       <c r="C253">
         <v>1</v>
@@ -14495,11 +13463,11 @@
       </c>
     </row>
     <row r="254" spans="1:15">
-      <c r="A254" t="s">
-        <v>267</v>
+      <c r="A254">
+        <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>650</v>
+        <v>259</v>
       </c>
       <c r="C254">
         <v>1</v>
@@ -14542,11 +13510,11 @@
       </c>
     </row>
     <row r="255" spans="1:15">
-      <c r="A255" t="s">
-        <v>268</v>
+      <c r="A255">
+        <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>651</v>
+        <v>260</v>
       </c>
       <c r="C255">
         <v>1</v>
@@ -14589,11 +13557,11 @@
       </c>
     </row>
     <row r="256" spans="1:15">
-      <c r="A256" t="s">
-        <v>269</v>
+      <c r="A256">
+        <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>652</v>
+        <v>261</v>
       </c>
       <c r="C256">
         <v>1</v>
@@ -14636,11 +13604,11 @@
       </c>
     </row>
     <row r="257" spans="1:15">
-      <c r="A257" t="s">
-        <v>270</v>
+      <c r="A257">
+        <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>653</v>
+        <v>262</v>
       </c>
       <c r="C257">
         <v>1</v>
@@ -14683,11 +13651,11 @@
       </c>
     </row>
     <row r="258" spans="1:15">
-      <c r="A258" t="s">
-        <v>271</v>
+      <c r="A258">
+        <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>654</v>
+        <v>263</v>
       </c>
       <c r="C258">
         <v>1</v>
@@ -14730,11 +13698,11 @@
       </c>
     </row>
     <row r="259" spans="1:15">
-      <c r="A259" t="s">
-        <v>272</v>
+      <c r="A259">
+        <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>655</v>
+        <v>264</v>
       </c>
       <c r="C259">
         <v>1</v>
@@ -14777,11 +13745,11 @@
       </c>
     </row>
     <row r="260" spans="1:15">
-      <c r="A260" t="s">
-        <v>273</v>
+      <c r="A260">
+        <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>656</v>
+        <v>265</v>
       </c>
       <c r="C260">
         <v>1</v>
@@ -14824,11 +13792,11 @@
       </c>
     </row>
     <row r="261" spans="1:15">
-      <c r="A261" t="s">
-        <v>274</v>
+      <c r="A261">
+        <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>657</v>
+        <v>266</v>
       </c>
       <c r="C261">
         <v>1</v>
@@ -14871,11 +13839,11 @@
       </c>
     </row>
     <row r="262" spans="1:15">
-      <c r="A262" t="s">
-        <v>275</v>
+      <c r="A262">
+        <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>658</v>
+        <v>267</v>
       </c>
       <c r="C262">
         <v>1</v>
@@ -14918,11 +13886,11 @@
       </c>
     </row>
     <row r="263" spans="1:15">
-      <c r="A263" t="s">
-        <v>276</v>
+      <c r="A263">
+        <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>659</v>
+        <v>268</v>
       </c>
       <c r="C263">
         <v>1</v>
@@ -14965,11 +13933,11 @@
       </c>
     </row>
     <row r="264" spans="1:15">
-      <c r="A264" t="s">
-        <v>277</v>
+      <c r="A264">
+        <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>660</v>
+        <v>269</v>
       </c>
       <c r="C264">
         <v>1</v>
@@ -15012,11 +13980,11 @@
       </c>
     </row>
     <row r="265" spans="1:15">
-      <c r="A265" t="s">
-        <v>278</v>
+      <c r="A265">
+        <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>661</v>
+        <v>270</v>
       </c>
       <c r="C265">
         <v>1</v>
@@ -15059,11 +14027,11 @@
       </c>
     </row>
     <row r="266" spans="1:15">
-      <c r="A266" t="s">
-        <v>279</v>
+      <c r="A266">
+        <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>662</v>
+        <v>271</v>
       </c>
       <c r="C266">
         <v>1</v>
@@ -15106,11 +14074,11 @@
       </c>
     </row>
     <row r="267" spans="1:15">
-      <c r="A267" t="s">
-        <v>280</v>
+      <c r="A267">
+        <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>663</v>
+        <v>272</v>
       </c>
       <c r="C267">
         <v>1</v>
@@ -15153,11 +14121,11 @@
       </c>
     </row>
     <row r="268" spans="1:15">
-      <c r="A268" t="s">
-        <v>281</v>
+      <c r="A268">
+        <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>664</v>
+        <v>273</v>
       </c>
       <c r="C268">
         <v>1</v>
@@ -15200,11 +14168,11 @@
       </c>
     </row>
     <row r="269" spans="1:15">
-      <c r="A269" t="s">
-        <v>282</v>
+      <c r="A269">
+        <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>665</v>
+        <v>274</v>
       </c>
       <c r="C269">
         <v>1</v>
@@ -15247,11 +14215,11 @@
       </c>
     </row>
     <row r="270" spans="1:15">
-      <c r="A270" t="s">
-        <v>283</v>
+      <c r="A270">
+        <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>666</v>
+        <v>275</v>
       </c>
       <c r="C270">
         <v>1</v>
@@ -15294,11 +14262,11 @@
       </c>
     </row>
     <row r="271" spans="1:15">
-      <c r="A271" t="s">
-        <v>284</v>
+      <c r="A271">
+        <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>667</v>
+        <v>276</v>
       </c>
       <c r="C271">
         <v>1</v>
@@ -15341,11 +14309,11 @@
       </c>
     </row>
     <row r="272" spans="1:15">
-      <c r="A272" t="s">
-        <v>285</v>
+      <c r="A272">
+        <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>668</v>
+        <v>277</v>
       </c>
       <c r="C272">
         <v>1</v>
@@ -15388,11 +14356,11 @@
       </c>
     </row>
     <row r="273" spans="1:15">
-      <c r="A273" t="s">
-        <v>286</v>
+      <c r="A273">
+        <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>669</v>
+        <v>278</v>
       </c>
       <c r="C273">
         <v>1</v>
@@ -15435,11 +14403,11 @@
       </c>
     </row>
     <row r="274" spans="1:15">
-      <c r="A274" t="s">
-        <v>287</v>
+      <c r="A274">
+        <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>670</v>
+        <v>279</v>
       </c>
       <c r="C274">
         <v>1</v>
@@ -15482,11 +14450,11 @@
       </c>
     </row>
     <row r="275" spans="1:15">
-      <c r="A275" t="s">
-        <v>288</v>
+      <c r="A275">
+        <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>671</v>
+        <v>280</v>
       </c>
       <c r="C275">
         <v>1</v>
@@ -15529,11 +14497,11 @@
       </c>
     </row>
     <row r="276" spans="1:15">
-      <c r="A276" t="s">
-        <v>289</v>
+      <c r="A276">
+        <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>672</v>
+        <v>281</v>
       </c>
       <c r="C276">
         <v>1</v>
@@ -15576,11 +14544,11 @@
       </c>
     </row>
     <row r="277" spans="1:15">
-      <c r="A277" t="s">
-        <v>290</v>
+      <c r="A277">
+        <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>673</v>
+        <v>282</v>
       </c>
       <c r="C277">
         <v>1</v>
@@ -15623,11 +14591,11 @@
       </c>
     </row>
     <row r="278" spans="1:15">
-      <c r="A278" t="s">
-        <v>291</v>
+      <c r="A278">
+        <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>674</v>
+        <v>283</v>
       </c>
       <c r="C278">
         <v>1</v>
@@ -15670,11 +14638,11 @@
       </c>
     </row>
     <row r="279" spans="1:15">
-      <c r="A279" t="s">
-        <v>292</v>
+      <c r="A279">
+        <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>675</v>
+        <v>284</v>
       </c>
       <c r="C279">
         <v>1</v>
@@ -15717,11 +14685,11 @@
       </c>
     </row>
     <row r="280" spans="1:15">
-      <c r="A280" t="s">
-        <v>293</v>
+      <c r="A280">
+        <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>676</v>
+        <v>285</v>
       </c>
       <c r="C280">
         <v>1</v>
@@ -15764,11 +14732,11 @@
       </c>
     </row>
     <row r="281" spans="1:15">
-      <c r="A281" t="s">
-        <v>294</v>
+      <c r="A281">
+        <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>677</v>
+        <v>286</v>
       </c>
       <c r="C281">
         <v>1</v>
@@ -15811,11 +14779,11 @@
       </c>
     </row>
     <row r="282" spans="1:15">
-      <c r="A282" t="s">
-        <v>295</v>
+      <c r="A282">
+        <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>678</v>
+        <v>287</v>
       </c>
       <c r="C282">
         <v>1</v>
@@ -15858,11 +14826,11 @@
       </c>
     </row>
     <row r="283" spans="1:15">
-      <c r="A283" t="s">
-        <v>296</v>
+      <c r="A283">
+        <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>679</v>
+        <v>288</v>
       </c>
       <c r="C283">
         <v>1</v>
@@ -15905,11 +14873,11 @@
       </c>
     </row>
     <row r="284" spans="1:15">
-      <c r="A284" t="s">
-        <v>297</v>
+      <c r="A284">
+        <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>680</v>
+        <v>289</v>
       </c>
       <c r="C284">
         <v>1</v>
@@ -15952,11 +14920,11 @@
       </c>
     </row>
     <row r="285" spans="1:15">
-      <c r="A285" t="s">
-        <v>298</v>
+      <c r="A285">
+        <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>681</v>
+        <v>290</v>
       </c>
       <c r="C285">
         <v>1</v>
@@ -15999,11 +14967,11 @@
       </c>
     </row>
     <row r="286" spans="1:15">
-      <c r="A286" t="s">
-        <v>299</v>
+      <c r="A286">
+        <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>682</v>
+        <v>291</v>
       </c>
       <c r="C286">
         <v>1</v>
@@ -16046,11 +15014,11 @@
       </c>
     </row>
     <row r="287" spans="1:15">
-      <c r="A287" t="s">
-        <v>300</v>
+      <c r="A287">
+        <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>683</v>
+        <v>292</v>
       </c>
       <c r="C287">
         <v>1</v>
@@ -16093,11 +15061,11 @@
       </c>
     </row>
     <row r="288" spans="1:15">
-      <c r="A288" t="s">
-        <v>301</v>
+      <c r="A288">
+        <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>684</v>
+        <v>293</v>
       </c>
       <c r="C288">
         <v>1</v>
@@ -16140,11 +15108,11 @@
       </c>
     </row>
     <row r="289" spans="1:15">
-      <c r="A289" t="s">
-        <v>302</v>
+      <c r="A289">
+        <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>685</v>
+        <v>294</v>
       </c>
       <c r="C289">
         <v>1</v>
@@ -16187,11 +15155,11 @@
       </c>
     </row>
     <row r="290" spans="1:15">
-      <c r="A290" t="s">
-        <v>303</v>
+      <c r="A290">
+        <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>686</v>
+        <v>295</v>
       </c>
       <c r="C290">
         <v>1</v>
@@ -16234,11 +15202,11 @@
       </c>
     </row>
     <row r="291" spans="1:15">
-      <c r="A291" t="s">
-        <v>304</v>
+      <c r="A291">
+        <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>687</v>
+        <v>296</v>
       </c>
       <c r="C291">
         <v>1</v>
@@ -16281,11 +15249,11 @@
       </c>
     </row>
     <row r="292" spans="1:15">
-      <c r="A292" t="s">
-        <v>305</v>
+      <c r="A292">
+        <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>688</v>
+        <v>297</v>
       </c>
       <c r="C292">
         <v>1</v>
@@ -16328,11 +15296,11 @@
       </c>
     </row>
     <row r="293" spans="1:15">
-      <c r="A293" t="s">
-        <v>306</v>
+      <c r="A293">
+        <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>689</v>
+        <v>298</v>
       </c>
       <c r="C293">
         <v>1</v>
@@ -16375,11 +15343,11 @@
       </c>
     </row>
     <row r="294" spans="1:15">
-      <c r="A294" t="s">
-        <v>307</v>
+      <c r="A294">
+        <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>690</v>
+        <v>299</v>
       </c>
       <c r="C294">
         <v>1</v>
@@ -16422,11 +15390,11 @@
       </c>
     </row>
     <row r="295" spans="1:15">
-      <c r="A295" t="s">
-        <v>308</v>
+      <c r="A295">
+        <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>691</v>
+        <v>300</v>
       </c>
       <c r="C295">
         <v>1</v>
@@ -16469,11 +15437,11 @@
       </c>
     </row>
     <row r="296" spans="1:15">
-      <c r="A296" t="s">
-        <v>309</v>
+      <c r="A296">
+        <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>692</v>
+        <v>301</v>
       </c>
       <c r="C296">
         <v>1</v>
@@ -16516,11 +15484,11 @@
       </c>
     </row>
     <row r="297" spans="1:15">
-      <c r="A297" t="s">
-        <v>310</v>
+      <c r="A297">
+        <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>693</v>
+        <v>302</v>
       </c>
       <c r="C297">
         <v>1</v>
@@ -16563,11 +15531,11 @@
       </c>
     </row>
     <row r="298" spans="1:15">
-      <c r="A298" t="s">
-        <v>311</v>
+      <c r="A298">
+        <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>694</v>
+        <v>303</v>
       </c>
       <c r="C298">
         <v>1</v>
@@ -16610,11 +15578,11 @@
       </c>
     </row>
     <row r="299" spans="1:15">
-      <c r="A299" t="s">
-        <v>312</v>
+      <c r="A299">
+        <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>695</v>
+        <v>304</v>
       </c>
       <c r="C299">
         <v>1</v>
@@ -16657,11 +15625,11 @@
       </c>
     </row>
     <row r="300" spans="1:15">
-      <c r="A300" t="s">
-        <v>313</v>
+      <c r="A300">
+        <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>696</v>
+        <v>305</v>
       </c>
       <c r="C300">
         <v>1</v>
@@ -16704,11 +15672,11 @@
       </c>
     </row>
     <row r="301" spans="1:15">
-      <c r="A301" t="s">
-        <v>314</v>
+      <c r="A301">
+        <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>697</v>
+        <v>306</v>
       </c>
       <c r="C301">
         <v>1</v>
@@ -16751,11 +15719,11 @@
       </c>
     </row>
     <row r="302" spans="1:15">
-      <c r="A302" t="s">
-        <v>315</v>
+      <c r="A302">
+        <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>698</v>
+        <v>307</v>
       </c>
       <c r="C302">
         <v>1</v>
@@ -16798,11 +15766,11 @@
       </c>
     </row>
     <row r="303" spans="1:15">
-      <c r="A303" t="s">
-        <v>316</v>
+      <c r="A303">
+        <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>699</v>
+        <v>308</v>
       </c>
       <c r="C303">
         <v>1</v>
@@ -16845,11 +15813,11 @@
       </c>
     </row>
     <row r="304" spans="1:15">
-      <c r="A304" t="s">
-        <v>317</v>
+      <c r="A304">
+        <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>700</v>
+        <v>309</v>
       </c>
       <c r="C304">
         <v>1</v>
@@ -16892,11 +15860,11 @@
       </c>
     </row>
     <row r="305" spans="1:15">
-      <c r="A305" t="s">
-        <v>318</v>
+      <c r="A305">
+        <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>701</v>
+        <v>310</v>
       </c>
       <c r="C305">
         <v>1</v>
@@ -16939,11 +15907,11 @@
       </c>
     </row>
     <row r="306" spans="1:15">
-      <c r="A306" t="s">
-        <v>319</v>
+      <c r="A306">
+        <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>702</v>
+        <v>311</v>
       </c>
       <c r="C306">
         <v>1</v>
@@ -16986,11 +15954,11 @@
       </c>
     </row>
     <row r="307" spans="1:15">
-      <c r="A307" t="s">
-        <v>320</v>
+      <c r="A307">
+        <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>703</v>
+        <v>312</v>
       </c>
       <c r="C307">
         <v>1</v>
@@ -17033,11 +16001,11 @@
       </c>
     </row>
     <row r="308" spans="1:15">
-      <c r="A308" t="s">
-        <v>321</v>
+      <c r="A308">
+        <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>704</v>
+        <v>313</v>
       </c>
       <c r="C308">
         <v>1</v>
@@ -17080,11 +16048,11 @@
       </c>
     </row>
     <row r="309" spans="1:15">
-      <c r="A309" t="s">
-        <v>322</v>
+      <c r="A309">
+        <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>705</v>
+        <v>314</v>
       </c>
       <c r="C309">
         <v>1</v>
@@ -17127,11 +16095,11 @@
       </c>
     </row>
     <row r="310" spans="1:15">
-      <c r="A310" t="s">
-        <v>323</v>
+      <c r="A310">
+        <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>706</v>
+        <v>315</v>
       </c>
       <c r="C310">
         <v>1</v>
@@ -17174,11 +16142,11 @@
       </c>
     </row>
     <row r="311" spans="1:15">
-      <c r="A311" t="s">
-        <v>324</v>
+      <c r="A311">
+        <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>707</v>
+        <v>316</v>
       </c>
       <c r="C311">
         <v>1</v>
@@ -17221,11 +16189,11 @@
       </c>
     </row>
     <row r="312" spans="1:15">
-      <c r="A312" t="s">
-        <v>325</v>
+      <c r="A312">
+        <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>708</v>
+        <v>317</v>
       </c>
       <c r="C312">
         <v>1</v>
@@ -17268,11 +16236,11 @@
       </c>
     </row>
     <row r="313" spans="1:15">
-      <c r="A313" t="s">
-        <v>326</v>
+      <c r="A313">
+        <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>709</v>
+        <v>318</v>
       </c>
       <c r="C313">
         <v>1</v>
@@ -17315,11 +16283,11 @@
       </c>
     </row>
     <row r="314" spans="1:15">
-      <c r="A314" t="s">
-        <v>327</v>
+      <c r="A314">
+        <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>710</v>
+        <v>319</v>
       </c>
       <c r="C314">
         <v>1</v>
@@ -17362,11 +16330,11 @@
       </c>
     </row>
     <row r="315" spans="1:15">
-      <c r="A315" t="s">
-        <v>328</v>
+      <c r="A315">
+        <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>711</v>
+        <v>320</v>
       </c>
       <c r="C315">
         <v>1</v>
@@ -17409,11 +16377,11 @@
       </c>
     </row>
     <row r="316" spans="1:15">
-      <c r="A316" t="s">
-        <v>329</v>
+      <c r="A316">
+        <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>712</v>
+        <v>321</v>
       </c>
       <c r="C316">
         <v>1</v>
@@ -17456,11 +16424,11 @@
       </c>
     </row>
     <row r="317" spans="1:15">
-      <c r="A317" t="s">
-        <v>330</v>
+      <c r="A317">
+        <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>713</v>
+        <v>322</v>
       </c>
       <c r="C317">
         <v>1</v>
@@ -17503,11 +16471,11 @@
       </c>
     </row>
     <row r="318" spans="1:15">
-      <c r="A318" t="s">
-        <v>331</v>
+      <c r="A318">
+        <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>714</v>
+        <v>323</v>
       </c>
       <c r="C318">
         <v>1</v>
@@ -17550,11 +16518,11 @@
       </c>
     </row>
     <row r="319" spans="1:15">
-      <c r="A319" t="s">
-        <v>332</v>
+      <c r="A319">
+        <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>715</v>
+        <v>324</v>
       </c>
       <c r="C319">
         <v>1</v>
@@ -17597,11 +16565,11 @@
       </c>
     </row>
     <row r="320" spans="1:15">
-      <c r="A320" t="s">
-        <v>333</v>
+      <c r="A320">
+        <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>716</v>
+        <v>325</v>
       </c>
       <c r="C320">
         <v>1</v>
@@ -17644,11 +16612,11 @@
       </c>
     </row>
     <row r="321" spans="1:15">
-      <c r="A321" t="s">
-        <v>334</v>
+      <c r="A321">
+        <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>717</v>
+        <v>326</v>
       </c>
       <c r="C321">
         <v>1</v>
@@ -17691,11 +16659,11 @@
       </c>
     </row>
     <row r="322" spans="1:15">
-      <c r="A322" t="s">
-        <v>335</v>
+      <c r="A322">
+        <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>718</v>
+        <v>327</v>
       </c>
       <c r="C322">
         <v>1</v>
@@ -17738,11 +16706,11 @@
       </c>
     </row>
     <row r="323" spans="1:15">
-      <c r="A323" t="s">
-        <v>336</v>
+      <c r="A323">
+        <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>719</v>
+        <v>328</v>
       </c>
       <c r="C323">
         <v>1</v>
@@ -17785,11 +16753,11 @@
       </c>
     </row>
     <row r="324" spans="1:15">
-      <c r="A324" t="s">
-        <v>337</v>
+      <c r="A324">
+        <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>720</v>
+        <v>329</v>
       </c>
       <c r="C324">
         <v>1</v>
@@ -17832,11 +16800,11 @@
       </c>
     </row>
     <row r="325" spans="1:15">
-      <c r="A325" t="s">
-        <v>338</v>
+      <c r="A325">
+        <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>721</v>
+        <v>330</v>
       </c>
       <c r="C325">
         <v>1</v>
@@ -17879,11 +16847,11 @@
       </c>
     </row>
     <row r="326" spans="1:15">
-      <c r="A326" t="s">
-        <v>339</v>
+      <c r="A326">
+        <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>722</v>
+        <v>331</v>
       </c>
       <c r="C326">
         <v>1</v>
@@ -17926,11 +16894,11 @@
       </c>
     </row>
     <row r="327" spans="1:15">
-      <c r="A327" t="s">
-        <v>340</v>
+      <c r="A327">
+        <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>723</v>
+        <v>332</v>
       </c>
       <c r="C327">
         <v>1</v>
@@ -17973,11 +16941,11 @@
       </c>
     </row>
     <row r="328" spans="1:15">
-      <c r="A328" t="s">
-        <v>341</v>
+      <c r="A328">
+        <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>724</v>
+        <v>333</v>
       </c>
       <c r="C328">
         <v>1</v>
@@ -18020,11 +16988,11 @@
       </c>
     </row>
     <row r="329" spans="1:15">
-      <c r="A329" t="s">
-        <v>342</v>
+      <c r="A329">
+        <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>725</v>
+        <v>334</v>
       </c>
       <c r="C329">
         <v>1</v>
@@ -18067,11 +17035,11 @@
       </c>
     </row>
     <row r="330" spans="1:15">
-      <c r="A330" t="s">
-        <v>343</v>
+      <c r="A330">
+        <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>726</v>
+        <v>335</v>
       </c>
       <c r="C330">
         <v>1</v>
@@ -18114,11 +17082,11 @@
       </c>
     </row>
     <row r="331" spans="1:15">
-      <c r="A331" t="s">
-        <v>344</v>
+      <c r="A331">
+        <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>727</v>
+        <v>336</v>
       </c>
       <c r="C331">
         <v>1</v>
@@ -18161,11 +17129,11 @@
       </c>
     </row>
     <row r="332" spans="1:15">
-      <c r="A332" t="s">
-        <v>345</v>
+      <c r="A332">
+        <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>728</v>
+        <v>337</v>
       </c>
       <c r="C332">
         <v>1</v>
@@ -18208,11 +17176,11 @@
       </c>
     </row>
     <row r="333" spans="1:15">
-      <c r="A333" t="s">
-        <v>346</v>
+      <c r="A333">
+        <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>729</v>
+        <v>338</v>
       </c>
       <c r="C333">
         <v>1</v>
@@ -18255,11 +17223,11 @@
       </c>
     </row>
     <row r="334" spans="1:15">
-      <c r="A334" t="s">
-        <v>347</v>
+      <c r="A334">
+        <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>730</v>
+        <v>339</v>
       </c>
       <c r="C334">
         <v>1</v>
@@ -18302,11 +17270,11 @@
       </c>
     </row>
     <row r="335" spans="1:15">
-      <c r="A335" t="s">
-        <v>348</v>
+      <c r="A335">
+        <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>731</v>
+        <v>340</v>
       </c>
       <c r="C335">
         <v>1</v>
@@ -18349,11 +17317,11 @@
       </c>
     </row>
     <row r="336" spans="1:15">
-      <c r="A336" t="s">
-        <v>349</v>
+      <c r="A336">
+        <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>732</v>
+        <v>341</v>
       </c>
       <c r="C336">
         <v>1</v>
@@ -18396,11 +17364,11 @@
       </c>
     </row>
     <row r="337" spans="1:15">
-      <c r="A337" t="s">
-        <v>350</v>
+      <c r="A337">
+        <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>733</v>
+        <v>342</v>
       </c>
       <c r="C337">
         <v>1</v>
@@ -18443,11 +17411,11 @@
       </c>
     </row>
     <row r="338" spans="1:15">
-      <c r="A338" t="s">
-        <v>351</v>
+      <c r="A338">
+        <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>734</v>
+        <v>343</v>
       </c>
       <c r="C338">
         <v>1</v>
@@ -18490,11 +17458,11 @@
       </c>
     </row>
     <row r="339" spans="1:15">
-      <c r="A339" t="s">
-        <v>352</v>
+      <c r="A339">
+        <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>735</v>
+        <v>344</v>
       </c>
       <c r="C339">
         <v>1</v>
@@ -18537,11 +17505,11 @@
       </c>
     </row>
     <row r="340" spans="1:15">
-      <c r="A340" t="s">
-        <v>353</v>
+      <c r="A340">
+        <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>736</v>
+        <v>345</v>
       </c>
       <c r="C340">
         <v>1</v>
@@ -18584,11 +17552,11 @@
       </c>
     </row>
     <row r="341" spans="1:15">
-      <c r="A341" t="s">
-        <v>354</v>
+      <c r="A341">
+        <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>737</v>
+        <v>346</v>
       </c>
       <c r="C341">
         <v>1</v>
@@ -18631,11 +17599,11 @@
       </c>
     </row>
     <row r="342" spans="1:15">
-      <c r="A342" t="s">
-        <v>355</v>
+      <c r="A342">
+        <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>738</v>
+        <v>347</v>
       </c>
       <c r="C342">
         <v>1</v>
@@ -18678,11 +17646,11 @@
       </c>
     </row>
     <row r="343" spans="1:15">
-      <c r="A343" t="s">
-        <v>356</v>
+      <c r="A343">
+        <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>739</v>
+        <v>348</v>
       </c>
       <c r="C343">
         <v>1</v>
@@ -18725,11 +17693,11 @@
       </c>
     </row>
     <row r="344" spans="1:15">
-      <c r="A344" t="s">
-        <v>357</v>
+      <c r="A344">
+        <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>740</v>
+        <v>349</v>
       </c>
       <c r="C344">
         <v>1</v>
@@ -18772,11 +17740,11 @@
       </c>
     </row>
     <row r="345" spans="1:15">
-      <c r="A345" t="s">
-        <v>358</v>
+      <c r="A345">
+        <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>740</v>
+        <v>349</v>
       </c>
       <c r="C345">
         <v>1</v>
@@ -18819,11 +17787,11 @@
       </c>
     </row>
     <row r="346" spans="1:15">
-      <c r="A346" t="s">
-        <v>359</v>
+      <c r="A346">
+        <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>741</v>
+        <v>350</v>
       </c>
       <c r="C346">
         <v>1</v>
@@ -18866,8 +17834,11 @@
       </c>
     </row>
     <row r="347" spans="1:15">
-      <c r="A347" t="s">
-        <v>360</v>
+      <c r="A347">
+        <v>345</v>
+      </c>
+      <c r="B347" t="s">
+        <v>351</v>
       </c>
       <c r="C347">
         <v>1</v>
@@ -18910,8 +17881,11 @@
       </c>
     </row>
     <row r="348" spans="1:15">
-      <c r="A348" t="s">
-        <v>361</v>
+      <c r="A348">
+        <v>346</v>
+      </c>
+      <c r="B348" t="s">
+        <v>352</v>
       </c>
       <c r="C348">
         <v>1</v>
@@ -18954,8 +17928,11 @@
       </c>
     </row>
     <row r="349" spans="1:15">
-      <c r="A349" t="s">
-        <v>362</v>
+      <c r="A349">
+        <v>347</v>
+      </c>
+      <c r="B349" t="s">
+        <v>353</v>
       </c>
       <c r="C349">
         <v>1</v>
@@ -18998,8 +17975,11 @@
       </c>
     </row>
     <row r="350" spans="1:15">
-      <c r="A350" t="s">
-        <v>363</v>
+      <c r="A350">
+        <v>348</v>
+      </c>
+      <c r="B350" t="s">
+        <v>354</v>
       </c>
       <c r="C350">
         <v>1</v>
@@ -19042,8 +18022,11 @@
       </c>
     </row>
     <row r="351" spans="1:15">
-      <c r="A351" t="s">
-        <v>364</v>
+      <c r="A351">
+        <v>349</v>
+      </c>
+      <c r="B351" t="s">
+        <v>355</v>
       </c>
       <c r="C351">
         <v>1</v>
@@ -19086,8 +18069,11 @@
       </c>
     </row>
     <row r="352" spans="1:15">
-      <c r="A352" t="s">
-        <v>365</v>
+      <c r="A352">
+        <v>350</v>
+      </c>
+      <c r="B352" t="s">
+        <v>356</v>
       </c>
       <c r="C352">
         <v>1</v>
@@ -19130,8 +18116,11 @@
       </c>
     </row>
     <row r="353" spans="1:15">
-      <c r="A353" t="s">
-        <v>366</v>
+      <c r="A353">
+        <v>351</v>
+      </c>
+      <c r="B353" t="s">
+        <v>357</v>
       </c>
       <c r="C353">
         <v>1</v>
@@ -19174,8 +18163,11 @@
       </c>
     </row>
     <row r="354" spans="1:15">
-      <c r="A354" t="s">
-        <v>367</v>
+      <c r="A354">
+        <v>352</v>
+      </c>
+      <c r="B354" t="s">
+        <v>358</v>
       </c>
       <c r="C354">
         <v>1</v>
@@ -19218,8 +18210,11 @@
       </c>
     </row>
     <row r="355" spans="1:15">
-      <c r="A355" t="s">
-        <v>368</v>
+      <c r="A355">
+        <v>353</v>
+      </c>
+      <c r="B355" t="s">
+        <v>359</v>
       </c>
       <c r="C355">
         <v>1</v>
@@ -19262,8 +18257,11 @@
       </c>
     </row>
     <row r="356" spans="1:15">
-      <c r="A356" t="s">
-        <v>369</v>
+      <c r="A356">
+        <v>354</v>
+      </c>
+      <c r="B356" t="s">
+        <v>360</v>
       </c>
       <c r="C356">
         <v>1</v>
@@ -19306,8 +18304,11 @@
       </c>
     </row>
     <row r="357" spans="1:15">
-      <c r="A357" t="s">
-        <v>370</v>
+      <c r="A357">
+        <v>355</v>
+      </c>
+      <c r="B357" t="s">
+        <v>361</v>
       </c>
       <c r="C357">
         <v>1</v>
@@ -19350,8 +18351,11 @@
       </c>
     </row>
     <row r="358" spans="1:15">
-      <c r="A358" t="s">
-        <v>371</v>
+      <c r="A358">
+        <v>356</v>
+      </c>
+      <c r="B358" t="s">
+        <v>362</v>
       </c>
       <c r="C358">
         <v>1</v>
@@ -19394,8 +18398,11 @@
       </c>
     </row>
     <row r="359" spans="1:15">
-      <c r="A359" t="s">
-        <v>372</v>
+      <c r="A359">
+        <v>357</v>
+      </c>
+      <c r="B359" t="s">
+        <v>363</v>
       </c>
       <c r="C359">
         <v>1</v>
@@ -19438,8 +18445,11 @@
       </c>
     </row>
     <row r="360" spans="1:15">
-      <c r="A360" t="s">
-        <v>373</v>
+      <c r="A360">
+        <v>358</v>
+      </c>
+      <c r="B360" t="s">
+        <v>364</v>
       </c>
       <c r="C360">
         <v>1</v>
@@ -19482,8 +18492,11 @@
       </c>
     </row>
     <row r="361" spans="1:15">
-      <c r="A361" t="s">
-        <v>374</v>
+      <c r="A361">
+        <v>359</v>
+      </c>
+      <c r="B361" t="s">
+        <v>365</v>
       </c>
       <c r="C361">
         <v>1</v>
@@ -19526,8 +18539,11 @@
       </c>
     </row>
     <row r="362" spans="1:15">
-      <c r="A362" t="s">
-        <v>375</v>
+      <c r="A362">
+        <v>360</v>
+      </c>
+      <c r="B362" t="s">
+        <v>366</v>
       </c>
       <c r="C362">
         <v>1</v>
@@ -19570,8 +18586,11 @@
       </c>
     </row>
     <row r="363" spans="1:15">
-      <c r="A363" t="s">
-        <v>376</v>
+      <c r="A363">
+        <v>361</v>
+      </c>
+      <c r="B363" t="s">
+        <v>367</v>
       </c>
       <c r="C363">
         <v>1</v>
@@ -19614,8 +18633,11 @@
       </c>
     </row>
     <row r="364" spans="1:15">
-      <c r="A364" t="s">
-        <v>377</v>
+      <c r="A364">
+        <v>362</v>
+      </c>
+      <c r="B364" t="s">
+        <v>368</v>
       </c>
       <c r="C364">
         <v>1</v>
@@ -19658,8 +18680,11 @@
       </c>
     </row>
     <row r="365" spans="1:15">
-      <c r="A365" t="s">
-        <v>378</v>
+      <c r="A365">
+        <v>363</v>
+      </c>
+      <c r="B365" t="s">
+        <v>369</v>
       </c>
       <c r="C365">
         <v>1</v>
@@ -19702,8 +18727,11 @@
       </c>
     </row>
     <row r="366" spans="1:15">
-      <c r="A366" t="s">
-        <v>379</v>
+      <c r="A366">
+        <v>364</v>
+      </c>
+      <c r="B366" t="s">
+        <v>370</v>
       </c>
       <c r="C366">
         <v>1</v>
@@ -19746,8 +18774,11 @@
       </c>
     </row>
     <row r="367" spans="1:15">
-      <c r="A367" t="s">
-        <v>380</v>
+      <c r="A367">
+        <v>365</v>
+      </c>
+      <c r="B367" t="s">
+        <v>371</v>
       </c>
       <c r="C367">
         <v>1</v>
@@ -19790,8 +18821,11 @@
       </c>
     </row>
     <row r="368" spans="1:15">
-      <c r="A368" t="s">
-        <v>381</v>
+      <c r="A368">
+        <v>366</v>
+      </c>
+      <c r="B368" t="s">
+        <v>372</v>
       </c>
       <c r="C368">
         <v>1</v>
@@ -19834,8 +18868,11 @@
       </c>
     </row>
     <row r="369" spans="1:15">
-      <c r="A369" t="s">
-        <v>382</v>
+      <c r="A369">
+        <v>367</v>
+      </c>
+      <c r="B369" t="s">
+        <v>373</v>
       </c>
       <c r="C369">
         <v>1</v>
@@ -19878,8 +18915,11 @@
       </c>
     </row>
     <row r="370" spans="1:15">
-      <c r="A370" t="s">
-        <v>383</v>
+      <c r="A370">
+        <v>368</v>
+      </c>
+      <c r="B370" t="s">
+        <v>374</v>
       </c>
       <c r="C370">
         <v>1</v>
@@ -19922,8 +18962,11 @@
       </c>
     </row>
     <row r="371" spans="1:15">
-      <c r="A371" t="s">
-        <v>384</v>
+      <c r="A371">
+        <v>369</v>
+      </c>
+      <c r="B371" t="s">
+        <v>375</v>
       </c>
       <c r="C371">
         <v>1</v>
@@ -19966,8 +19009,11 @@
       </c>
     </row>
     <row r="372" spans="1:15">
-      <c r="A372" t="s">
-        <v>385</v>
+      <c r="A372">
+        <v>370</v>
+      </c>
+      <c r="B372" t="s">
+        <v>376</v>
       </c>
       <c r="C372">
         <v>1</v>
@@ -20010,8 +19056,11 @@
       </c>
     </row>
     <row r="373" spans="1:15">
-      <c r="A373" t="s">
-        <v>386</v>
+      <c r="A373">
+        <v>371</v>
+      </c>
+      <c r="B373" t="s">
+        <v>377</v>
       </c>
       <c r="C373">
         <v>1</v>
@@ -20054,8 +19103,11 @@
       </c>
     </row>
     <row r="374" spans="1:15">
-      <c r="A374" t="s">
-        <v>387</v>
+      <c r="A374">
+        <v>372</v>
+      </c>
+      <c r="B374" t="s">
+        <v>378</v>
       </c>
       <c r="C374">
         <v>1</v>
@@ -20098,8 +19150,11 @@
       </c>
     </row>
     <row r="375" spans="1:15">
-      <c r="A375" t="s">
-        <v>388</v>
+      <c r="A375">
+        <v>373</v>
+      </c>
+      <c r="B375" t="s">
+        <v>379</v>
       </c>
       <c r="C375">
         <v>1</v>
@@ -20142,8 +19197,11 @@
       </c>
     </row>
     <row r="376" spans="1:15">
-      <c r="A376" t="s">
-        <v>389</v>
+      <c r="A376">
+        <v>374</v>
+      </c>
+      <c r="B376" t="s">
+        <v>380</v>
       </c>
       <c r="C376">
         <v>1</v>
@@ -20186,8 +19244,11 @@
       </c>
     </row>
     <row r="377" spans="1:15">
-      <c r="A377" t="s">
-        <v>390</v>
+      <c r="A377">
+        <v>375</v>
+      </c>
+      <c r="B377" t="s">
+        <v>381</v>
       </c>
       <c r="C377">
         <v>1</v>
@@ -20230,8 +19291,11 @@
       </c>
     </row>
     <row r="378" spans="1:15">
-      <c r="A378" t="s">
-        <v>391</v>
+      <c r="A378">
+        <v>376</v>
+      </c>
+      <c r="B378" t="s">
+        <v>382</v>
       </c>
       <c r="C378">
         <v>1</v>
@@ -20274,8 +19338,11 @@
       </c>
     </row>
     <row r="379" spans="1:15">
-      <c r="A379" t="s">
-        <v>392</v>
+      <c r="A379">
+        <v>377</v>
+      </c>
+      <c r="B379" t="s">
+        <v>383</v>
       </c>
       <c r="C379">
         <v>1</v>
@@ -20318,8 +19385,11 @@
       </c>
     </row>
     <row r="380" spans="1:15">
-      <c r="A380" t="s">
-        <v>393</v>
+      <c r="A380">
+        <v>378</v>
+      </c>
+      <c r="B380" t="s">
+        <v>384</v>
       </c>
       <c r="C380">
         <v>1</v>
@@ -20362,8 +19432,11 @@
       </c>
     </row>
     <row r="381" spans="1:15">
-      <c r="A381" t="s">
-        <v>394</v>
+      <c r="A381">
+        <v>379</v>
+      </c>
+      <c r="B381" t="s">
+        <v>385</v>
       </c>
       <c r="C381">
         <v>1</v>
@@ -20406,8 +19479,11 @@
       </c>
     </row>
     <row r="382" spans="1:15">
-      <c r="A382" t="s">
-        <v>395</v>
+      <c r="A382">
+        <v>380</v>
+      </c>
+      <c r="B382" t="s">
+        <v>386</v>
       </c>
       <c r="C382">
         <v>1</v>
@@ -20450,8 +19526,11 @@
       </c>
     </row>
     <row r="383" spans="1:15">
-      <c r="A383" t="s">
-        <v>396</v>
+      <c r="A383">
+        <v>381</v>
+      </c>
+      <c r="B383" t="s">
+        <v>387</v>
       </c>
       <c r="C383">
         <v>1</v>
@@ -20494,8 +19573,11 @@
       </c>
     </row>
     <row r="384" spans="1:15">
-      <c r="A384" t="s">
-        <v>397</v>
+      <c r="A384">
+        <v>382</v>
+      </c>
+      <c r="B384" t="s">
+        <v>388</v>
       </c>
       <c r="C384">
         <v>1</v>
@@ -20538,8 +19620,11 @@
       </c>
     </row>
     <row r="385" spans="1:15">
-      <c r="A385" t="s">
-        <v>398</v>
+      <c r="A385">
+        <v>383</v>
+      </c>
+      <c r="B385" t="s">
+        <v>389</v>
       </c>
       <c r="C385">
         <v>1</v>
@@ -20582,8 +19667,11 @@
       </c>
     </row>
     <row r="386" spans="1:15">
-      <c r="A386" t="s">
-        <v>399</v>
+      <c r="A386">
+        <v>384</v>
+      </c>
+      <c r="B386" t="s">
+        <v>390</v>
       </c>
       <c r="C386">
         <v>1</v>
@@ -20626,8 +19714,11 @@
       </c>
     </row>
     <row r="387" spans="1:15">
-      <c r="A387" t="s">
-        <v>400</v>
+      <c r="A387">
+        <v>385</v>
+      </c>
+      <c r="B387" t="s">
+        <v>391</v>
       </c>
       <c r="C387">
         <v>1</v>
@@ -20670,8 +19761,11 @@
       </c>
     </row>
     <row r="388" spans="1:15">
-      <c r="A388" t="s">
-        <v>401</v>
+      <c r="A388">
+        <v>386</v>
+      </c>
+      <c r="B388" t="s">
+        <v>392</v>
       </c>
       <c r="C388">
         <v>1</v>
@@ -20714,8 +19808,11 @@
       </c>
     </row>
     <row r="389" spans="1:15">
-      <c r="A389" t="s">
-        <v>402</v>
+      <c r="A389">
+        <v>387</v>
+      </c>
+      <c r="B389" t="s">
+        <v>393</v>
       </c>
       <c r="C389">
         <v>1</v>
@@ -20758,8 +19855,11 @@
       </c>
     </row>
     <row r="390" spans="1:15">
-      <c r="A390" t="s">
-        <v>403</v>
+      <c r="A390">
+        <v>388</v>
+      </c>
+      <c r="B390" t="s">
+        <v>394</v>
       </c>
       <c r="C390">
         <v>1</v>
@@ -20802,8 +19902,11 @@
       </c>
     </row>
     <row r="391" spans="1:15">
-      <c r="A391" t="s">
-        <v>404</v>
+      <c r="A391">
+        <v>389</v>
+      </c>
+      <c r="B391" t="s">
+        <v>395</v>
       </c>
       <c r="C391">
         <v>1</v>
@@ -20846,8 +19949,11 @@
       </c>
     </row>
     <row r="392" spans="1:15">
-      <c r="A392" t="s">
-        <v>405</v>
+      <c r="A392">
+        <v>390</v>
+      </c>
+      <c r="B392" t="s">
+        <v>396</v>
       </c>
       <c r="C392">
         <v>1</v>
@@ -20890,8 +19996,11 @@
       </c>
     </row>
     <row r="393" spans="1:15">
-      <c r="A393" t="s">
-        <v>406</v>
+      <c r="A393">
+        <v>391</v>
+      </c>
+      <c r="B393" t="s">
+        <v>397</v>
       </c>
       <c r="C393">
         <v>1</v>
